--- a/data/florida-marine-businesses.xlsx
+++ b/data/florida-marine-businesses.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="FL Marine Businesses" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'FL Marine Businesses'!$A$1:$I$214</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'FL Marine Businesses'!$A$1:$I$210</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I214"/>
+  <dimension ref="A1:I210"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -573,28 +573,20 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Allied Marine</t>
+          <t>Sandy Hook Yachts</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Boat sales</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>(239) 262-6500</t>
-        </is>
-      </c>
+          <t>Boat builder</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>https://www.alliedmarine.com/</t>
-        </is>
-      </c>
+      <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>909 10th Street South, Naples, FL 34102</t>
+          <t>2072 Davis Boulevard, Naples, FL 34104</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -604,109 +596,73 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=26.1375005,-81.7918287</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=26.1379673,-81.7789323</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/13931285591</t>
+          <t>https://www.openstreetmap.org/way/523951593</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Atlantic Marine</t>
+          <t>Trident Pontoons</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Boat sales</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>(386) 788-1644</t>
-        </is>
-      </c>
+          <t>Boat builder</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>https://www.atlanticmarinefl.com/</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>520 Dunlawton Avenue, Port Orange, FL 32129</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Port Orange</t>
-        </is>
-      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=29.1416364,-80.993227</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=28.7662459,-81.7514748</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/926456586</t>
+          <t>https://www.openstreetmap.org/node/13423206895</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Casual Monday Charters</t>
+          <t>Young Boats, Inc.</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Boat sales</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>(305) 988-1179</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>CasualMondayCharters@gmail.com</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>https://casualmondaycharters.com/</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>5950 Peninsular Avenue, Key West, FL 33040</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Key West</t>
-        </is>
-      </c>
+          <t>Boat builder</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=24.5636631,-81.7300407</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=29.037232,-82.668107</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/13344455911</t>
+          <t>https://www.openstreetmap.org/node/2326076177</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Formula Boats</t>
+          <t>Allied Marine</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -716,13 +672,13 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>(239) 331-2104</t>
+          <t>(239) 262-6500</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
-          <t>http://www.formulaboatssouth.com/</t>
+          <t>https://www.alliedmarine.com/</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -737,19 +693,19 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=26.137523,-81.791648</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=26.1375005,-81.7918287</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/13931285592</t>
+          <t>https://www.openstreetmap.org/node/13931285591</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Galati Yacht Sales</t>
+          <t>Allwater Marine</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -757,38 +713,38 @@
           <t>Boat sales</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>(941) 778-0755</t>
-        </is>
-      </c>
+      <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>https://allwatermarine.com/</t>
+        </is>
+      </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>900 South Bay Boulevard, Anna Maria, FL 34216</t>
+          <t>2751 Avenue of the America, Englewood, FL 34224</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Anna Maria</t>
+          <t>Englewood</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=27.5273013,-82.7215854</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=26.9174485,-82.3090515</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/644621074</t>
+          <t>https://www.openstreetmap.org/node/13411413245</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Germain Yachts Center</t>
+          <t>Atlantic Marine</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -798,40 +754,40 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>(239) 262-2628</t>
+          <t>(386) 788-1644</t>
         </is>
       </c>
       <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
-          <t>https://www.germainyachts.com/</t>
+          <t>https://www.atlanticmarinefl.com/</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>895 10th Street South, Naples, FL 34102</t>
+          <t>520 Dunlawton Avenue, Port Orange, FL 32129</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Naples</t>
+          <t>Port Orange</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=26.1377551,-81.7923362</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=29.1416364,-80.993227</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/13931285593</t>
+          <t>https://www.openstreetmap.org/way/926456586</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Hinckley Yachts</t>
+          <t>Casual Monday Charters</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -841,40 +797,44 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>(239) 300-4995</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr"/>
+          <t>(305) 988-1179</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>CasualMondayCharters@gmail.com</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>https://www.hinckleyyachts.com/contact/sales/</t>
+          <t>https://casualmondaycharters.com/</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>535 5th Avenue South, Naples, FL 34102</t>
+          <t>5950 Peninsular Avenue, Key West, FL 33040</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Naples</t>
+          <t>Key West</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=26.141451,-81.7998456</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=24.5636631,-81.7300407</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/9407924119</t>
+          <t>https://www.openstreetmap.org/node/13344455911</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MarineMax</t>
+          <t>Formula Boats</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -884,18 +844,18 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>(239) 963-8108</t>
+          <t>(239) 331-2104</t>
         </is>
       </c>
       <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>https://www.marinemax.com/stores/yachts-and-charter</t>
+          <t>http://www.formulaboatssouth.com/</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>525 5th Avenue South, Naples, FL 34102</t>
+          <t>909 10th Street South, Naples, FL 34102</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -905,19 +865,19 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=26.1414336,-81.8000192</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=26.137523,-81.791648</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/9407861916</t>
+          <t>https://www.openstreetmap.org/node/13931285592</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Miley's Diesel Service, Inc.</t>
+          <t>Galati Yacht Sales</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -927,40 +887,36 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>(239) 728-2217</t>
+          <t>(941) 778-0755</t>
         </is>
       </c>
       <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>https://www.mileysdiesel.com</t>
-        </is>
-      </c>
+      <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>10821 Sunset Plaza Circle, Fort Myers, FL 33908</t>
+          <t>900 South Bay Boulevard, Anna Maria, FL 34216</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Fort Myers</t>
+          <t>Anna Maria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=26.4899551,-81.9307834</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=27.5273013,-82.7215854</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/12641867668</t>
+          <t>https://www.openstreetmap.org/way/644621074</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>PartsVu</t>
+          <t>Germain Yachts Center</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -970,40 +926,40 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>(888) 625-5460</t>
+          <t>(239) 262-2628</t>
         </is>
       </c>
       <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
-          <t>https://www.partsvu.com/</t>
+          <t>https://www.germainyachts.com/</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>111 Triple Diamond Boulevard, Venice, FL 34275</t>
+          <t>895 10th Street South, Naples, FL 34102</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Venice</t>
+          <t>Naples</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=27.1461492,-82.4043859</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=26.1377551,-81.7923362</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/11486939216</t>
+          <t>https://www.openstreetmap.org/node/13931285593</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Pier 41 Marine</t>
+          <t>Hinckley Yachts</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1013,40 +969,40 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>(239) 790-5797</t>
+          <t>(239) 300-4995</t>
         </is>
       </c>
       <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
-          <t>https://www.pier41marine.com/</t>
+          <t>https://www.hinckleyyachts.com/contact/sales/</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>15650 S Tamiami Trail, Fort Myers, FL 33908</t>
+          <t>535 5th Avenue South, Naples, FL 34102</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fort Myers</t>
+          <t>Naples</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=26.5131936,-81.864748</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=26.141451,-81.7998456</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/11743403700</t>
+          <t>https://www.openstreetmap.org/node/9407924119</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Pinned Up Performance</t>
+          <t>Marine Trading Post</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1054,42 +1010,38 @@
           <t>Boat sales</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>(727) 717-3401</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>pinnedupperformance@gmail.com</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>https://marinetradingpost.com</t>
+        </is>
+      </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>6841 Amberjack Lane, Hudson, FL 34667</t>
+          <t>4694 Tamiami Trail, Port Charlotte, FL</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hudson</t>
+          <t>Port Charlotte</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=28.3468676,-82.7005723</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=26.9603075,-82.0683645</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/13740317686</t>
+          <t>https://www.openstreetmap.org/way/956109779</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Plantation Boat Mart &amp; Marina</t>
+          <t>MarineMax</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1099,44 +1051,40 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>(305) 852-5424</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>info@plantationboat.com</t>
-        </is>
-      </c>
+          <t>(239) 963-8108</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
-          <t>https://www.plantationboat.com/</t>
+          <t>https://www.marinemax.com/stores/yachts-and-charter</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>90400 Overseas Highway, Tavernier, FL 33070</t>
+          <t>525 5th Avenue South, Naples, FL 34102</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Tavernier</t>
+          <t>Naples</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=25.0013539,-80.5374475</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=26.1414336,-81.8000192</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/962266931</t>
+          <t>https://www.openstreetmap.org/node/9407861916</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Skip's Marina</t>
+          <t>Miley's Diesel Service, Inc.</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1146,40 +1094,40 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>(941) 777-4727</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>skipsbaitandtackle@yahoo.com</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr"/>
+          <t>(239) 728-2217</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>https://www.mileysdiesel.com</t>
+        </is>
+      </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1990 Placida Road, Englewood, FL 34223</t>
+          <t>10821 Sunset Plaza Circle, Fort Myers, FL 33908</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Englewood</t>
+          <t>Fort Myers</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=26.9315316,-82.3371595</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=26.4899551,-81.9307834</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/13622978100</t>
+          <t>https://www.openstreetmap.org/node/12641867668</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>West Marine</t>
+          <t>Naples Marina Sales</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1187,46 +1135,30 @@
           <t>Boat sales</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>(386) 255-2013</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>wmCustomerService@westmarine.com</t>
-        </is>
-      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>https://www.westmarine.com/stores/daytona-beach-fl-1313</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>1300 International Speedway Boulevard, Daytona Beach, FL 32114</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>Daytona Beach</t>
-        </is>
-      </c>
+          <t>https://www.naplesmarina.com/</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=29.1987693,-81.0553745</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=26.0791465,-81.7234218</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/3655764080</t>
+          <t>https://www.openstreetmap.org/node/5524144554</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>West Marine</t>
+          <t>PartsVu</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1236,40 +1168,40 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>(941) 625-2700</t>
+          <t>(888) 625-5460</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>https://www.westmarine.com/stores/port-charlotte-fl-155/</t>
+          <t>https://www.partsvu.com/</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>4265 Tamiami Trail, Port Charlotte, FL 33980</t>
+          <t>111 Triple Diamond Boulevard, Venice, FL 34275</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Port Charlotte</t>
+          <t>Venice</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=26.9665132,-82.0793925</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=27.1461492,-82.4043859</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/12750666121</t>
+          <t>https://www.openstreetmap.org/node/11486939216</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>WMF Watercraft &amp; Marine</t>
+          <t>Pier 41 Marine</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1279,935 +1211,811 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>(239) 573-6256</t>
+          <t>(239) 790-5797</t>
         </is>
       </c>
       <c r="D20" t="inlineStr"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>https://www.wmfwatercraft.com/</t>
+          <t>https://www.pier41marine.com/</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1037 Southwest Pine Island Road, Cape Coral, FL 33991</t>
+          <t>15650 S Tamiami Trail, Fort Myers, FL 33908</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Cape Coral</t>
+          <t>Fort Myers</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=26.6441944,-81.9960597</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=26.5131936,-81.864748</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/10747621566</t>
+          <t>https://www.openstreetmap.org/node/11743403700</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>15th Street Marina Marathon (at Boot Key Harbor)</t>
+          <t>Pinned Up Performance</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Marina / docks</t>
+          <t>Boat sales</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>(305) 393-0383</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>https://www.bootkeymarina.com/</t>
-        </is>
-      </c>
+          <t>(727) 717-3401</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>pinnedupperformance@gmail.com</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>890 15th Street Ocean, Marathon, FL 33050</t>
+          <t>6841 Amberjack Lane, Hudson, FL 34667</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Marathon</t>
+          <t>Hudson</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=24.7062565,-81.1082023</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=28.3468676,-82.7005723</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/8922500078</t>
+          <t>https://www.openstreetmap.org/node/13740317686</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>All Water Excursions Marina</t>
+          <t>Plantation Boat Mart &amp; Marina</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Marina / docks</t>
+          <t>Boat sales</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>(239) 594-0213</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr"/>
+          <t>(305) 852-5424</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>info@plantationboat.com</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>https://allwaterexcursionsmarina.com/</t>
+          <t>https://www.plantationboat.com/</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>12345 Tamiami Trail N, Naples, FL 34110</t>
+          <t>90400 Overseas Highway, Tavernier, FL 33070</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Naples</t>
+          <t>Tavernier</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=26.2829502,-81.8022954</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=25.0013539,-80.5374475</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/6417384864</t>
+          <t>https://www.openstreetmap.org/way/962266931</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Battery Park Marina</t>
+          <t>Skip's Marina</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Marina / docks</t>
+          <t>Boat sales</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>(850) 653-9319</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr"/>
+          <t>(941) 777-4727</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>skipsbaitandtackle@yahoo.com</t>
+        </is>
+      </c>
       <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>1990 Placida Road, Englewood, FL 34223</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Englewood</t>
+        </is>
+      </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=29.7230508,-84.9823741</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=26.9315316,-82.3371595</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/4744964936</t>
+          <t>https://www.openstreetmap.org/node/13622978100</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Blackfin Resort and Marina</t>
+          <t>Tampa Bay Marine Center</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Marina / docks</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>(305) 743-2393</t>
-        </is>
-      </c>
+          <t>Boat sales</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr"/>
       <c r="E24" t="inlineStr">
         <is>
-          <t>https://www.blackfinresort.com/</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
+          <t>www.TBmarinecenter.com</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>8478 Seminole Boulevard, Seminole, FL 33772</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Seminole</t>
+        </is>
+      </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=24.7169137,-81.0829727</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=27.8494942,-82.7875314</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/8928642214</t>
+          <t>https://www.openstreetmap.org/way/280618826</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Bud n'Mary's Marina</t>
+          <t>Walker's Yacht Sales</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Marina / docks</t>
+          <t>Boat sales</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>info@budnmarys.com</t>
-        </is>
-      </c>
+      <c r="D25" t="inlineStr"/>
       <c r="E25" t="inlineStr">
         <is>
-          <t>https://www.budnmarys.com/</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>79851 Overseas Highway, Islamorada, FL 33036</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Islamorada</t>
-        </is>
-      </c>
+          <t>http://walkersmarine.com/</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr"/>
+      <c r="G25" t="inlineStr"/>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=24.897636,-80.6576988</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=26.5070699,-81.9430706</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/965364676</t>
+          <t>https://www.openstreetmap.org/node/5565776036</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Caloosa Cove Resort &amp; Marina</t>
+          <t>West Marine</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Marina / docks</t>
+          <t>Boat sales</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>(305) 664-4455</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr"/>
+          <t>(386) 255-2013</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>wmCustomerService@westmarine.com</t>
+        </is>
+      </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>https://caloosacove.com/</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
+          <t>https://www.westmarine.com/stores/daytona-beach-fl-1313</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>1300 International Speedway Boulevard, Daytona Beach, FL 32114</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Daytona Beach</t>
+        </is>
+      </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=24.8491927,-80.7377951</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=29.1987693,-81.0553745</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/8928678682</t>
+          <t>https://www.openstreetmap.org/node/3655764080</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>City of Fort Myers Yacht Basin</t>
+          <t>West Marine</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Marina / docks</t>
+          <t>Boat sales</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>(239) 321-7080</t>
+          <t>(941) 625-2700</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>https://www.westmarine.com/stores/port-charlotte-fl-155/</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>4265 Tamiami Trail, Port Charlotte, FL 33980</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Port Charlotte</t>
+        </is>
+      </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=26.6476634,-81.8693038</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=26.9665132,-82.0793925</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/340302977</t>
+          <t>https://www.openstreetmap.org/node/12750666121</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Crescent Fish Camp</t>
+          <t>WMF Watercraft &amp; Marine</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Marina / docks</t>
+          <t>Boat sales</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>(386) 698-2444</t>
+          <t>(239) 573-6256</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" t="inlineStr">
         <is>
-          <t>https://outdooradventureretreats.com/crescent-fish-camp/</t>
+          <t>https://www.wmfwatercraft.com/</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>100 Grove Avenue, Crescent City, FL 32112</t>
+          <t>1037 Southwest Pine Island Road, Cape Coral, FL 33991</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Crescent City</t>
+          <t>Cape Coral</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=29.4436575,-81.5076064</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=26.6441944,-81.9960597</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/1184702288</t>
+          <t>https://www.openstreetmap.org/node/10747621566</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Duck Key Marina</t>
+          <t>Boat House</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Marina / docks</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>(305) 289-0161</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>BoatStorage@MarinaDuckKey.com</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>https://marinaduckkey.com/</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>1149 Greenbriar Road, Duck Key, FL 33050</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Duck Key</t>
-        </is>
-      </c>
+          <t>Boat sales</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr"/>
+      <c r="G29" t="inlineStr"/>
       <c r="H29" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=24.7747609,-80.9158341</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=26.1387893,-81.7737369</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/3059042376</t>
+          <t>https://www.openstreetmap.org/node/14001331662</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Faro Blanco Resort &amp; Yacht Club</t>
+          <t>Boater's World</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Marina / docks</t>
+          <t>Boat sales</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>marina@faroblancoresort.com</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>https://www.faroblancoresort.com/</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>5412 State Road 64 E, Bradenton, FL 34208</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Bradenton</t>
+        </is>
+      </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=24.710771,-81.1049165</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=27.4932139,-82.4936238</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/960749909</t>
+          <t>https://www.openstreetmap.org/way/547760369</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Freedom Boat Club</t>
+          <t>Boaters Paradise</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Marina / docks</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>(888) 781-7363</t>
-        </is>
-      </c>
+          <t>Boat sales</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
       <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>https://freedomboatclub.com/locations/4-venice-fl/</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>990 La Guna Drive, Venice, FL 34285</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Venice</t>
-        </is>
-      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr"/>
       <c r="H31" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=27.105446,-82.4611904</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=26.6439102,-81.9958193</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/673173186</t>
+          <t>https://www.openstreetmap.org/node/8499225849</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Inn Marine</t>
+          <t>Capstan Yachts</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Marina / docks</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>(941) 964-4620</t>
-        </is>
-      </c>
+          <t>Boat sales</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
       <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>https://the-gasparilla-inn.com/activities/marina/</t>
-        </is>
-      </c>
+      <c r="E32" t="inlineStr"/>
       <c r="F32" t="inlineStr">
         <is>
-          <t>891 8th Street East, Boca Grande, FL 33921</t>
+          <t>1100 6th Avenue South, Naples, FL 34102</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Boca Grande</t>
+          <t>Naples</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=26.7548844,-82.2602885</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=26.1401217,-81.7918785</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/964358197</t>
+          <t>https://www.openstreetmap.org/node/13230505773</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Loggerhead Marina Daytona Beach</t>
+          <t>Dealer's Choice</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Marina / docks</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>(386) 523-3100</t>
-        </is>
-      </c>
+          <t>Boat sales</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
       <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>www.loggerheaddaytonabeach.com</t>
-        </is>
-      </c>
+      <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>721 Ballough Road, Daytona Beach, 32114</t>
+          <t>5980 Lakehurst Drive, Orlando, FL</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Daytona Beach</t>
+          <t>Orlando</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=29.2259811,-81.0228833</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=28.452092,-81.4616428</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/2841956238</t>
+          <t>https://www.openstreetmap.org/way/141130579</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Loggerhead Marina Saint Pete</t>
+          <t>Endless Seas Boat Sales</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Marina / docks</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>(727) 867-2600</t>
-        </is>
-      </c>
+          <t>Boat sales</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
       <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>https://loggerheadmarina.com/</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>5821 32nd Way South, Saint Petersburg, FL 33712</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>Saint Petersburg</t>
-        </is>
-      </c>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr"/>
+      <c r="G34" t="inlineStr"/>
       <c r="H34" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=27.7136989,-82.6779452</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=27.8105495,-82.7563041</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/174953456</t>
+          <t>https://www.openstreetmap.org/node/4184366920</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Marlin Bay Resort &amp; Marina</t>
+          <t>Jet-Ski Repair</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Marina / docks</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>(305) 731-2207</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>concierge@marlinbay.com</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>https://www.marlinbay.com/</t>
-        </is>
-      </c>
+          <t>Boat sales</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>3800 Gulfview Avenue, FL 33050</t>
+          <t>1301 Pasadena Avenue South</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
       <c r="H35" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=24.7159004,-81.0908627</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=27.7564542,-82.7373941</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/8928610265</t>
+          <t>https://www.openstreetmap.org/way/243780501</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>O'Neil's Marina</t>
+          <t>Kayaks</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Marina / docks</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>(727) 867-2585</t>
-        </is>
-      </c>
+          <t>Boat sales</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
       <c r="D36" t="inlineStr"/>
       <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>6701 Sunshine Skyway Lane South, Saint Petersburg, FL 33711</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>Saint Petersburg</t>
-        </is>
-      </c>
+      <c r="F36" t="inlineStr"/>
+      <c r="G36" t="inlineStr"/>
       <c r="H36" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=27.7074959,-82.6805545</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=27.7705916,-82.7293372</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/473381997</t>
+          <t>https://www.openstreetmap.org/node/2030817866</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Ocean Club Marina Port Canaveral</t>
+          <t>Lake Area Watersports</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Marina / docks</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>(321) 783-9001</t>
-        </is>
-      </c>
+          <t>Boat sales</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
       <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>https://oceanclubmarina-pc.com/</t>
-        </is>
-      </c>
+      <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>930 Mullet Road, Port Canaveral, 32920</t>
+          <t>829 State Highway 21, Melrose, FL 32666</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Port Canaveral</t>
+          <t>Melrose</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=28.4071344,-80.629588</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=29.7082923,-82.0442786</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/2842015453</t>
+          <t>https://www.openstreetmap.org/way/749312825</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sea Dog Charters Marina</t>
+          <t>LTD Motors Auto, RV, &amp; Marine Center</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Marina / docks</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>(305) 743-8255</t>
-        </is>
-      </c>
+          <t>Boat sales</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
       <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>https://seadogcharters.net</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>1248 Overseas Highway, Marathon, FL 33050</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>Marathon</t>
-        </is>
-      </c>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr"/>
+      <c r="G38" t="inlineStr"/>
       <c r="H38" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=24.7091585,-81.1117446</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=28.8934984,-82.5843792</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/3060499556</t>
+          <t>https://www.openstreetmap.org/node/7044384283</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Snake Creek Marina</t>
+          <t>Madiera Marine Sales</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Marina / docks</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>(305) 396-7724</t>
-        </is>
-      </c>
+          <t>Boat sales</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
       <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>https://snakecreekmarinakeys.com/</t>
-        </is>
-      </c>
+      <c r="E39" t="inlineStr"/>
       <c r="F39" t="inlineStr">
         <is>
-          <t>85401 Overseas Highway, Islamorada, FL 33036</t>
+          <t>6869 Park Boulevard, Pinellas Park</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Islamorada</t>
+          <t>Pinellas Park</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=24.9504129,-80.5912068</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=27.8394723,-82.7332575</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/3058696699</t>
+          <t>https://www.openstreetmap.org/way/274097975</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Snell Isle Marina</t>
+          <t>MarineMax Fort Myers</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Marina / docks</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>(727) 895-8142</t>
-        </is>
-      </c>
+          <t>Boat sales</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
       <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>https://www.spyc.com/</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>1305 Snell Isle Boulevard NE, Saint Petersburg, FL 33704</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>Saint Petersburg</t>
-        </is>
-      </c>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr"/>
+      <c r="G40" t="inlineStr"/>
       <c r="H40" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=27.799719,-82.610148</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=26.5385857,-81.9203657</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/1951987506</t>
+          <t>https://www.openstreetmap.org/node/5563398749</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Telemar Bay Marina</t>
+          <t>Mitchell Marine</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Marina / docks</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>(321) 773-2468</t>
-        </is>
-      </c>
+          <t>Boat sales</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
       <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>https://telemarbaymarina.com/</t>
-        </is>
-      </c>
+      <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>1399 Banana River Drive, Indian Harbour Beach, FL 32937</t>
+          <t>6789 Ulmerton Road, Largo, FL 33771</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Indian Harbour Beach</t>
+          <t>Largo</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=28.1492468,-80.6042632</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=27.8945834,-82.7319894</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/9345106335</t>
+          <t>https://www.openstreetmap.org/way/217914135</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Uncle Henry's Marina</t>
+          <t>Naples Boat Mart</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Marina / docks</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>(941) 964-0154</t>
-        </is>
-      </c>
+          <t>Boat sales</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
       <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>http://www.unclehenrysmarina.com/</t>
-        </is>
-      </c>
+      <c r="E42" t="inlineStr"/>
       <c r="F42" t="inlineStr"/>
       <c r="G42" t="inlineStr"/>
       <c r="H42" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=26.8032655,-82.2753503</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=26.1610691,-81.7662084</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/964050069</t>
+          <t>https://www.openstreetmap.org/node/6751933958</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Sandy Hook Yachts</t>
+          <t>Quality Boats</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Boat builder</t>
+          <t>Boat sales</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
@@ -2215,34 +2023,34 @@
       <c r="E43" t="inlineStr"/>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2072 Davis Boulevard, Naples, FL 34104</t>
+          <t>17389 US 19, Largo, FL 33760</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Naples</t>
+          <t>Largo</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=26.1379673,-81.7789323</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=27.930694,-82.729675</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/523951593</t>
+          <t>https://www.openstreetmap.org/node/1769622295</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Trident Pontoons</t>
+          <t>Route 1 Motorsports</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Boat builder</t>
+          <t>Boat sales</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
@@ -2252,24 +2060,24 @@
       <c r="G44" t="inlineStr"/>
       <c r="H44" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=28.7662459,-81.7514748</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=28.0049773,-80.5651931</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/13423206895</t>
+          <t>https://www.openstreetmap.org/node/7343561418</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Young Boats, Inc.</t>
+          <t>Saint Pete Powersports</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Boat builder</t>
+          <t>Boat sales</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
@@ -2279,19 +2087,19 @@
       <c r="G45" t="inlineStr"/>
       <c r="H45" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=29.037232,-82.668107</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=27.7649415,-82.6800367</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/2326076177</t>
+          <t>https://www.openstreetmap.org/way/280373609</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Allwater Marine</t>
+          <t>San Carlos Marine</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -2301,36 +2109,24 @@
       </c>
       <c r="C46" t="inlineStr"/>
       <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>https://allwatermarine.com/</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>2751 Avenue of the America, Englewood, FL 34224</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>Englewood</t>
-        </is>
-      </c>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr"/>
+      <c r="G46" t="inlineStr"/>
       <c r="H46" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=26.9174485,-82.3090515</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=26.6569467,-81.8463067</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/13411413245</t>
+          <t>https://www.openstreetmap.org/way/939609010</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Boat House</t>
+          <t>Sea Base Ship Store</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2345,19 +2141,19 @@
       <c r="G47" t="inlineStr"/>
       <c r="H47" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=26.1387893,-81.7737369</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=24.8509814,-80.7387526</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/14001331662</t>
+          <t>https://www.openstreetmap.org/way/690293084</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Boater's World</t>
+          <t>The Boat Place</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2368,31 +2164,23 @@
       <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr"/>
       <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>5412 State Road 64 E, Bradenton, FL 34208</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>Bradenton</t>
-        </is>
-      </c>
+      <c r="F48" t="inlineStr"/>
+      <c r="G48" t="inlineStr"/>
       <c r="H48" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=27.4932139,-82.4936238</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=26.5029342,-81.9440818</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/547760369</t>
+          <t>https://www.openstreetmap.org/node/5565776035</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Boaters Paradise</t>
+          <t>Walker's Marine</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -2407,19 +2195,19 @@
       <c r="G49" t="inlineStr"/>
       <c r="H49" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=26.6439102,-81.9958193</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=26.1387398,-81.769505</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/8499225849</t>
+          <t>https://www.openstreetmap.org/node/14001331630</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Capstan Yachts</t>
+          <t>West Marine</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -2432,29 +2220,29 @@
       <c r="E50" t="inlineStr"/>
       <c r="F50" t="inlineStr">
         <is>
-          <t>1100 6th Avenue South, Naples, FL 34102</t>
+          <t>2109 Overseas Highway, Marathon, 33050</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Naples</t>
+          <t>Marathon</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=26.1401217,-81.7918785</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=24.7086124,-81.1035697</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/13230505773</t>
+          <t>https://www.openstreetmap.org/way/302535565</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Dealer's Choice</t>
+          <t>West Marine</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -2467,29 +2255,29 @@
       <c r="E51" t="inlineStr"/>
       <c r="F51" t="inlineStr">
         <is>
-          <t>5980 Lakehurst Drive, Orlando, FL</t>
+          <t>3905 West Cypress Street, Tampa, FL 33607</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Orlando</t>
+          <t>Tampa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=28.452092,-81.4616428</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=27.9525568,-82.5079927</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/141130579</t>
+          <t>https://www.openstreetmap.org/way/524314469</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Endless Seas Boat Sales</t>
+          <t>World Cat</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -2504,782 +2292,906 @@
       <c r="G52" t="inlineStr"/>
       <c r="H52" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=27.8105495,-82.7563041</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=26.1388697,-81.7713398</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/4184366920</t>
+          <t>https://www.openstreetmap.org/node/14001331633</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Formula Boats</t>
+          <t>15th Street Marina Marathon (at Boot Key Harbor)</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Boat sales</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr"/>
+          <t>Marina / docks</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>(305) 393-0383</t>
+        </is>
+      </c>
       <c r="D53" t="inlineStr"/>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>https://www.bootkeymarina.com/</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>890 15th Street Ocean, Marathon, FL 33050</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=26.1474355,-81.7931086</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=24.7062565,-81.1082023</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/13713863641</t>
+          <t>https://www.openstreetmap.org/node/8922500078</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Jet-Ski Repair</t>
+          <t>A &amp; B Marina</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Boat sales</t>
+          <t>Marina / docks</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
       <c r="D54" t="inlineStr"/>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>1301 Pasadena Avenue South</t>
-        </is>
-      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>https://www.aandbmarina.com/</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
       <c r="G54" t="inlineStr"/>
       <c r="H54" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=27.7564542,-82.7373941</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=24.5618016,-81.8029104</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/243780501</t>
+          <t>https://www.openstreetmap.org/way/960082399</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Kayaks</t>
+          <t>All Water Excursions Marina</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Boat sales</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr"/>
+          <t>Marina / docks</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>(239) 594-0213</t>
+        </is>
+      </c>
       <c r="D55" t="inlineStr"/>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>https://allwaterexcursionsmarina.com/</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>12345 Tamiami Trail N, Naples, FL 34110</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Naples</t>
+        </is>
+      </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=27.7705916,-82.7293372</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=26.2829502,-81.8022954</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/2030817866</t>
+          <t>https://www.openstreetmap.org/node/6417384864</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Lake Area Watersports</t>
+          <t>Banana Bay Resort &amp; Marina</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Boat sales</t>
+          <t>Marina / docks</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
       <c r="D56" t="inlineStr"/>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>829 State Highway 21, Melrose, FL 32666</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>Melrose</t>
-        </is>
-      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>https://www.bhotelsandresorts.com/banana-bay/</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+      <c r="G56" t="inlineStr"/>
       <c r="H56" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=29.7082923,-82.0442786</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=24.7169478,-81.0845031</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/749312825</t>
+          <t>https://www.openstreetmap.org/node/8928599380</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>LTD Motors Auto, RV, &amp; Marine Center</t>
+          <t>Battery Park Marina</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Boat sales</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr"/>
+          <t>Marina / docks</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>(850) 653-9319</t>
+        </is>
+      </c>
       <c r="D57" t="inlineStr"/>
       <c r="E57" t="inlineStr"/>
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr"/>
       <c r="H57" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=28.8934984,-82.5843792</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=29.7230508,-84.9823741</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/7044384283</t>
+          <t>https://www.openstreetmap.org/node/4744964936</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Madiera Marine Sales</t>
+          <t>Bayside Marina</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Boat sales</t>
+          <t>Marina / docks</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
       <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>6869 Park Boulevard, Pinellas Park</t>
-        </is>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>Pinellas Park</t>
-        </is>
-      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>https://stores.basspro.com/us/fl/islamorada/81576-overseas-highway-22264191.html</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+      <c r="G58" t="inlineStr"/>
       <c r="H58" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=27.8394723,-82.7332575</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=24.9155738,-80.6401628</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/274097975</t>
+          <t>https://www.openstreetmap.org/way/396013568</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Marine Trading Post</t>
+          <t>Blackfin Resort and Marina</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Boat sales</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr"/>
+          <t>Marina / docks</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>(305) 743-2393</t>
+        </is>
+      </c>
       <c r="D59" t="inlineStr"/>
       <c r="E59" t="inlineStr">
         <is>
-          <t>https://marinetradingpost.com</t>
-        </is>
-      </c>
-      <c r="F59" t="inlineStr">
-        <is>
-          <t>4694 Tamiami Trail, Port Charlotte, FL</t>
-        </is>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>Port Charlotte</t>
-        </is>
-      </c>
+          <t>https://www.blackfinresort.com/</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+      <c r="G59" t="inlineStr"/>
       <c r="H59" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=26.9603075,-82.0683645</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=24.7169137,-81.0829727</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/956109779</t>
+          <t>https://www.openstreetmap.org/node/8928642214</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>MarineMax</t>
+          <t>Bonita Bay Marina</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Boat sales</t>
+          <t>Marina / docks</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
       <c r="D60" t="inlineStr"/>
-      <c r="E60" t="inlineStr"/>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>https://www.bonitabaymarina.net/</t>
+        </is>
+      </c>
       <c r="F60" t="inlineStr"/>
       <c r="G60" t="inlineStr"/>
       <c r="H60" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=26.1409689,-81.791219</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=26.3390025,-81.8280455</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/13485359875</t>
+          <t>https://www.openstreetmap.org/node/1928559347</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>MarineMax Fort Myers</t>
+          <t>Bradenton Yacht Club</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Boat sales</t>
+          <t>Marina / docks</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
       <c r="D61" t="inlineStr"/>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr"/>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>https://www.bradentonyachtclub.com/</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>4307 Snead Island Road, Palmetto, 34211</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Palmetto</t>
+        </is>
+      </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=26.5385857,-81.9203657</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=27.5251018,-82.6117991</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/5563398749</t>
+          <t>https://www.openstreetmap.org/node/2390747716</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Mitchell Marine</t>
+          <t>Bud n'Mary's Marina</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Boat sales</t>
+          <t>Marina / docks</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
-      <c r="D62" t="inlineStr"/>
-      <c r="E62" t="inlineStr"/>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>info@budnmarys.com</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>https://www.budnmarys.com/</t>
+        </is>
+      </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>6789 Ulmerton Road, Largo, FL 33771</t>
+          <t>79851 Overseas Highway, Islamorada, FL 33036</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Largo</t>
+          <t>Islamorada</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=27.8945834,-82.7319894</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=24.897636,-80.6576988</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/217914135</t>
+          <t>https://www.openstreetmap.org/way/965364676</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Naples Boat Mart</t>
+          <t>Caloosa Cove Resort &amp; Marina</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Boat sales</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr"/>
+          <t>Marina / docks</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>(305) 664-4455</t>
+        </is>
+      </c>
       <c r="D63" t="inlineStr"/>
-      <c r="E63" t="inlineStr"/>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>https://caloosacove.com/</t>
+        </is>
+      </c>
       <c r="F63" t="inlineStr"/>
       <c r="G63" t="inlineStr"/>
       <c r="H63" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=26.1610691,-81.7662084</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=24.8491927,-80.7377951</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/6751933958</t>
+          <t>https://www.openstreetmap.org/node/8928678682</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Naples Marina Sales</t>
+          <t>Captain Hook's Marina &amp; Dive Center</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Boat sales</t>
+          <t>Marina / docks</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
       <c r="D64" t="inlineStr"/>
       <c r="E64" t="inlineStr">
         <is>
-          <t>https://www.naplesmarina.com/</t>
-        </is>
-      </c>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr"/>
+          <t>https://captainhooks.com/</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>11833 Overseas Highway, Marathon, FL 33050</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=26.0791465,-81.7234218</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=24.7299949,-81.0304125</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/5524144554</t>
+          <t>https://www.openstreetmap.org/node/3060410108</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Quality Boats</t>
+          <t>Captain Hook's Marina and Dive Center</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Boat sales</t>
+          <t>Marina / docks</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
       <c r="D65" t="inlineStr"/>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>17389 US 19, Largo, FL 33760</t>
-        </is>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>Largo</t>
-        </is>
-      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>https://captainhooks.com/</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr"/>
+      <c r="G65" t="inlineStr"/>
       <c r="H65" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=27.930694,-82.729675</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=24.7298344,-81.0301698</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/1769622295</t>
+          <t>https://www.openstreetmap.org/way/962640922</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Route 1 Motorsports</t>
+          <t>Caribee Boat Sales &amp; Marina</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Boat sales</t>
+          <t>Marina / docks</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
       <c r="D66" t="inlineStr"/>
-      <c r="E66" t="inlineStr"/>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>https://www.caribeeboats.com/</t>
+        </is>
+      </c>
       <c r="F66" t="inlineStr"/>
       <c r="G66" t="inlineStr"/>
       <c r="H66" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=28.0049773,-80.5651931</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=24.9183449,-80.636662</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/7343561418</t>
+          <t>https://www.openstreetmap.org/way/965392909</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Saint Pete Powersports</t>
+          <t>City of Fort Myers Yacht Basin</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Boat sales</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr"/>
+          <t>Marina / docks</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>(239) 321-7080</t>
+        </is>
+      </c>
       <c r="D67" t="inlineStr"/>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="inlineStr"/>
       <c r="G67" t="inlineStr"/>
       <c r="H67" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=27.7649415,-82.6800367</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=26.6476634,-81.8693038</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/280373609</t>
+          <t>https://www.openstreetmap.org/way/340302977</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>San Carlos Marine</t>
+          <t>Conch Harbor Marina</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Boat sales</t>
+          <t>Marina / docks</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
       <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr"/>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>https://conchharbormarina.com/</t>
+        </is>
+      </c>
       <c r="F68" t="inlineStr"/>
       <c r="G68" t="inlineStr"/>
       <c r="H68" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=26.6569467,-81.8463067</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=24.5628708,-81.8001401</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/939609010</t>
+          <t>https://www.openstreetmap.org/way/960095386</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sea Base Ship Store</t>
+          <t>Coral Bay Marina</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Boat sales</t>
+          <t>Marina / docks</t>
         </is>
       </c>
       <c r="C69" t="inlineStr"/>
       <c r="D69" t="inlineStr"/>
-      <c r="E69" t="inlineStr"/>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>https://coral-bay-marina.com/</t>
+        </is>
+      </c>
       <c r="F69" t="inlineStr"/>
       <c r="G69" t="inlineStr"/>
       <c r="H69" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=24.8509814,-80.7387526</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=24.9198675,-80.6356235</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/690293084</t>
+          <t>https://www.openstreetmap.org/node/3058734961</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Tampa Bay Marine Center</t>
+          <t>Crescent Fish Camp</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Boat sales</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr"/>
+          <t>Marina / docks</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>(386) 698-2444</t>
+        </is>
+      </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" t="inlineStr">
         <is>
-          <t>www.TBmarinecenter.com</t>
+          <t>https://outdooradventureretreats.com/crescent-fish-camp/</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>8478 Seminole Boulevard, Seminole, FL 33772</t>
+          <t>100 Grove Avenue, Crescent City, FL 32112</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Seminole</t>
+          <t>Crescent City</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=27.8494942,-82.7875314</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=29.4436575,-81.5076064</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/280618826</t>
+          <t>https://www.openstreetmap.org/way/1184702288</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>The Boat Place</t>
+          <t>Davis Islands Yacht Club</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Boat sales</t>
+          <t>Marina / docks</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
       <c r="D71" t="inlineStr"/>
-      <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr"/>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>https://www.diyc.org/</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>1315 Severn Avenue, Tampa, FL 33606</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Tampa</t>
+        </is>
+      </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=26.5029342,-81.9440818</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=27.9083573,-82.4499825</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/5565776035</t>
+          <t>https://www.openstreetmap.org/way/28937844</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Walker's Marine</t>
+          <t>Duck Key Marina</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Boat sales</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr"/>
-      <c r="D72" t="inlineStr"/>
-      <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr"/>
+          <t>Marina / docks</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>(305) 289-0161</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>BoatStorage@MarinaDuckKey.com</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>https://marinaduckkey.com/</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>1149 Greenbriar Road, Duck Key, FL 33050</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Duck Key</t>
+        </is>
+      </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=26.1387398,-81.769505</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=24.7747609,-80.9158341</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/14001331630</t>
+          <t>https://www.openstreetmap.org/node/3059042376</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Walker's Yacht Sales</t>
+          <t>Faro Blanco Resort &amp; Yacht Club</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Boat sales</t>
+          <t>Marina / docks</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
-      <c r="D73" t="inlineStr"/>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>marina@faroblancoresort.com</t>
+        </is>
+      </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>http://walkersmarine.com/</t>
+          <t>https://www.faroblancoresort.com/</t>
         </is>
       </c>
       <c r="F73" t="inlineStr"/>
       <c r="G73" t="inlineStr"/>
       <c r="H73" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=26.5070699,-81.9430706</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=24.710771,-81.1049165</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/5565776036</t>
+          <t>https://www.openstreetmap.org/way/960749909</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>West Marine</t>
+          <t>Free Marina Day Slips</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Boat sales</t>
+          <t>Marina / docks</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
       <c r="D74" t="inlineStr"/>
-      <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>81984 overseas highway</t>
-        </is>
-      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>https://www.sanfordfl.gov/residents/marina-day-slips-1500</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr"/>
       <c r="G74" t="inlineStr"/>
       <c r="H74" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=25.9540211,-81.7226825</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=28.8152803,-81.2677706</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/4814486457</t>
+          <t>https://www.openstreetmap.org/node/8934027328</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>West Marine</t>
+          <t>Freedom Boat Club</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Boat sales</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr"/>
+          <t>Marina / docks</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>(888) 781-7363</t>
+        </is>
+      </c>
       <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>https://freedomboatclub.com/locations/4-venice-fl/</t>
+        </is>
+      </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2109 Overseas Highway, Marathon, 33050</t>
+          <t>990 La Guna Drive, Venice, FL 34285</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Marathon</t>
+          <t>Venice</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=24.7086124,-81.1035697</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=27.105446,-82.4611904</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/302535565</t>
+          <t>https://www.openstreetmap.org/way/673173186</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>West Marine</t>
+          <t>Galleon Marina</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Boat sales</t>
+          <t>Marina / docks</t>
         </is>
       </c>
       <c r="C76" t="inlineStr"/>
       <c r="D76" t="inlineStr"/>
-      <c r="E76" t="inlineStr"/>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>3905 West Cypress Street, Tampa, FL 33607</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>Tampa</t>
-        </is>
-      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>https://www.galleonmarinakeywest.com/</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr"/>
+      <c r="G76" t="inlineStr"/>
       <c r="H76" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=27.9525568,-82.5079927</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=24.5624049,-81.8029456</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/524314469</t>
+          <t>https://www.openstreetmap.org/way/960077345</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>World Cat</t>
+          <t>Hawks Cay Resort Marina</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Boat sales</t>
+          <t>Marina / docks</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
       <c r="D77" t="inlineStr"/>
-      <c r="E77" t="inlineStr"/>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>https://www.hawkscay.com/amenities/hawks-cay-marina</t>
+        </is>
+      </c>
       <c r="F77" t="inlineStr"/>
       <c r="G77" t="inlineStr"/>
       <c r="H77" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=26.1388697,-81.7713398</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=24.7779182,-80.9131337</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/14001331633</t>
+          <t>https://www.openstreetmap.org/node/8922857152</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>A &amp; B Marina</t>
+          <t>Inn Marine</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -3287,30 +3199,42 @@
           <t>Marina / docks</t>
         </is>
       </c>
-      <c r="C78" t="inlineStr"/>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>(941) 964-4620</t>
+        </is>
+      </c>
       <c r="D78" t="inlineStr"/>
       <c r="E78" t="inlineStr">
         <is>
-          <t>https://www.aandbmarina.com/</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr"/>
-      <c r="G78" t="inlineStr"/>
+          <t>https://the-gasparilla-inn.com/activities/marina/</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>891 8th Street East, Boca Grande, FL 33921</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Boca Grande</t>
+        </is>
+      </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=24.5618016,-81.8029104</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=26.7548844,-82.2602885</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/960082399</t>
+          <t>https://www.openstreetmap.org/way/964358197</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Adventure Yacht Harbor Marina</t>
+          <t>IslaMarina</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -3320,24 +3244,28 @@
       </c>
       <c r="C79" t="inlineStr"/>
       <c r="D79" t="inlineStr"/>
-      <c r="E79" t="inlineStr"/>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>https://islamarinakeys.com/</t>
+        </is>
+      </c>
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr"/>
       <c r="H79" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=29.1320088,-80.9618291</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=24.9535923,-80.5855417</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/488741075</t>
+          <t>https://www.openstreetmap.org/way/965374081</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Anclote Village Marina</t>
+          <t>Key West Bight Marina</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -3347,24 +3275,28 @@
       </c>
       <c r="C80" t="inlineStr"/>
       <c r="D80" t="inlineStr"/>
-      <c r="E80" t="inlineStr"/>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>https://www.keywestbightmarina.com/</t>
+        </is>
+      </c>
       <c r="F80" t="inlineStr"/>
       <c r="G80" t="inlineStr"/>
       <c r="H80" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=28.1729981,-82.7856812</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=24.5619147,-81.8016413</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/1024429087</t>
+          <t>https://www.openstreetmap.org/way/83579780</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Bahia Honda Marina</t>
+          <t>Loggerhead Marina Daytona Beach</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -3372,26 +3304,42 @@
           <t>Marina / docks</t>
         </is>
       </c>
-      <c r="C81" t="inlineStr"/>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>(386) 523-3100</t>
+        </is>
+      </c>
       <c r="D81" t="inlineStr"/>
-      <c r="E81" t="inlineStr"/>
-      <c r="F81" t="inlineStr"/>
-      <c r="G81" t="inlineStr"/>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>www.loggerheaddaytonabeach.com</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>721 Ballough Road, Daytona Beach, 32114</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Daytona Beach</t>
+        </is>
+      </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=24.6570071,-81.2783212</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=29.2259811,-81.0228833</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/323507973</t>
+          <t>https://www.openstreetmap.org/node/2841956238</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Banana Bay Resort &amp; Marina</t>
+          <t>Loggerhead Marina Saint Pete</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -3399,30 +3347,42 @@
           <t>Marina / docks</t>
         </is>
       </c>
-      <c r="C82" t="inlineStr"/>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>(727) 867-2600</t>
+        </is>
+      </c>
       <c r="D82" t="inlineStr"/>
       <c r="E82" t="inlineStr">
         <is>
-          <t>https://www.bhotelsandresorts.com/banana-bay/</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr"/>
-      <c r="G82" t="inlineStr"/>
+          <t>https://loggerheadmarina.com/</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>5821 32nd Way South, Saint Petersburg, FL 33712</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Saint Petersburg</t>
+        </is>
+      </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=24.7169478,-81.0845031</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=27.7136989,-82.6779452</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/8928599380</t>
+          <t>https://www.openstreetmap.org/way/174953456</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Bay Pines Marina</t>
+          <t>Marathon Marina &amp; Boat Yard</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -3432,24 +3392,28 @@
       </c>
       <c r="C83" t="inlineStr"/>
       <c r="D83" t="inlineStr"/>
-      <c r="E83" t="inlineStr"/>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>https://marathonmarinaresort.com</t>
+        </is>
+      </c>
       <c r="F83" t="inlineStr"/>
       <c r="G83" t="inlineStr"/>
       <c r="H83" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=27.8153949,-82.765832</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=24.7046204,-81.1121887</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/2346847950</t>
+          <t>https://www.openstreetmap.org/way/962279125</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Bayfront Marina (Turtle Beach Marina)</t>
+          <t>Marlin Bay Resort &amp; Marina</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -3457,26 +3421,42 @@
           <t>Marina / docks</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr"/>
-      <c r="D84" t="inlineStr"/>
-      <c r="E84" t="inlineStr"/>
-      <c r="F84" t="inlineStr"/>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>(305) 731-2207</t>
+        </is>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>concierge@marlinbay.com</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>https://www.marlinbay.com/</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>3800 Gulfview Avenue, FL 33050</t>
+        </is>
+      </c>
       <c r="G84" t="inlineStr"/>
       <c r="H84" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=27.2201456,-82.5143547</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=24.7159004,-81.0908627</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/5930370144</t>
+          <t>https://www.openstreetmap.org/node/8928610265</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Bayside Marina</t>
+          <t>Maximo Marina - Saint Petersburg/Tampa</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -3488,26 +3468,26 @@
       <c r="D85" t="inlineStr"/>
       <c r="E85" t="inlineStr">
         <is>
-          <t>https://stores.basspro.com/us/fl/islamorada/81576-overseas-highway-22264191.html</t>
+          <t>http://www.igy-maximomarina.com/</t>
         </is>
       </c>
       <c r="F85" t="inlineStr"/>
       <c r="G85" t="inlineStr"/>
       <c r="H85" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=28.3693258,-81.5581119</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=27.7243732,-82.6823903</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/295164413</t>
+          <t>https://www.openstreetmap.org/way/609719332</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Bonita Bay Marina</t>
+          <t>Monroe Harbour Marina</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -3519,26 +3499,26 @@
       <c r="D86" t="inlineStr"/>
       <c r="E86" t="inlineStr">
         <is>
-          <t>https://www.bonitabaymarina.net/</t>
+          <t>http://www.monroeharbour.com/</t>
         </is>
       </c>
       <c r="F86" t="inlineStr"/>
       <c r="G86" t="inlineStr"/>
       <c r="H86" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=26.3390025,-81.8280455</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=28.8150946,-81.2668498</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/1928559347</t>
+          <t>https://www.openstreetmap.org/way/964718295</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Boot Key Harbor Marathon City Marina</t>
+          <t>Municipal Marina</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -3548,24 +3528,28 @@
       </c>
       <c r="C87" t="inlineStr"/>
       <c r="D87" t="inlineStr"/>
-      <c r="E87" t="inlineStr"/>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>https://www.dunedingov.com/index.aspx?page=151</t>
+        </is>
+      </c>
       <c r="F87" t="inlineStr"/>
       <c r="G87" t="inlineStr"/>
       <c r="H87" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=24.7097864,-81.091419</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=28.0124558,-82.7922848</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/589379803</t>
+          <t>https://www.openstreetmap.org/way/523224923</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Bradenton Yacht Club</t>
+          <t>O'Neil's Marina</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3573,38 +3557,38 @@
           <t>Marina / docks</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr"/>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>(727) 867-2585</t>
+        </is>
+      </c>
       <c r="D88" t="inlineStr"/>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>https://www.bradentonyachtclub.com/</t>
-        </is>
-      </c>
+      <c r="E88" t="inlineStr"/>
       <c r="F88" t="inlineStr">
         <is>
-          <t>4307 Snead Island Road, Palmetto, 34211</t>
+          <t>6701 Sunshine Skyway Lane South, Saint Petersburg, FL 33711</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Palmetto</t>
+          <t>Saint Petersburg</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=27.5251018,-82.6117991</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=27.7074959,-82.6805545</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/2390747716</t>
+          <t>https://www.openstreetmap.org/way/473381997</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Brookside Marina</t>
+          <t>Oasis Marina</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
@@ -3614,24 +3598,28 @@
       </c>
       <c r="C89" t="inlineStr"/>
       <c r="D89" t="inlineStr"/>
-      <c r="E89" t="inlineStr"/>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>https://www.oasismarinas.com/</t>
+        </is>
+      </c>
       <c r="F89" t="inlineStr"/>
       <c r="G89" t="inlineStr"/>
       <c r="H89" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=26.1395604,-81.77943</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=24.5643553,-81.7375146</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/1537009881</t>
+          <t>https://www.openstreetmap.org/relation/15741992</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Burnt Store Marina</t>
+          <t>Ocean Club Marina Port Canaveral</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
@@ -3639,26 +3627,42 @@
           <t>Marina / docks</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr"/>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>(321) 783-9001</t>
+        </is>
+      </c>
       <c r="D90" t="inlineStr"/>
-      <c r="E90" t="inlineStr"/>
-      <c r="F90" t="inlineStr"/>
-      <c r="G90" t="inlineStr"/>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>https://oceanclubmarina-pc.com/</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>930 Mullet Road, Port Canaveral, 32920</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Port Canaveral</t>
+        </is>
+      </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=26.7627883,-82.0586868</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=28.4071344,-80.629588</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/relation/8721197</t>
+          <t>https://www.openstreetmap.org/node/2842015453</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Caloosa Yacht &amp; Racquet Club Marina</t>
+          <t>Oceans Edge Resort &amp; Marina Key West</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
@@ -3668,24 +3672,36 @@
       </c>
       <c r="C91" t="inlineStr"/>
       <c r="D91" t="inlineStr"/>
-      <c r="E91" t="inlineStr"/>
-      <c r="F91" t="inlineStr"/>
-      <c r="G91" t="inlineStr"/>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>https://www.oceansedgekeywest.com/</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>5950 Peninsular Avenue, Key West, FL 33040</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Key West</t>
+        </is>
+      </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=26.5642781,-81.9184075</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=24.5631903,-81.7298505</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/2160330791</t>
+          <t>https://www.openstreetmap.org/way/415309284</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Calusa Island Marina &amp; Yacht Club</t>
+          <t>Pete's Pier Marina</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
@@ -3695,24 +3711,28 @@
       </c>
       <c r="C92" t="inlineStr"/>
       <c r="D92" t="inlineStr"/>
-      <c r="E92" t="inlineStr"/>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>https://www.petespier.com</t>
+        </is>
+      </c>
       <c r="F92" t="inlineStr"/>
       <c r="G92" t="inlineStr"/>
       <c r="H92" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=25.9197202,-81.6514363</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=28.8948545,-82.597468</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/relation/8422119</t>
+          <t>https://www.openstreetmap.org/node/11813178785</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Cape Coral Yacht Club</t>
+          <t>Plantation Yacht Harbor Marina</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
@@ -3722,24 +3742,28 @@
       </c>
       <c r="C93" t="inlineStr"/>
       <c r="D93" t="inlineStr"/>
-      <c r="E93" t="inlineStr"/>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>https://www.islamorada.fl.us/</t>
+        </is>
+      </c>
       <c r="F93" t="inlineStr"/>
       <c r="G93" t="inlineStr"/>
       <c r="H93" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=26.5428428,-81.9514457</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=24.9648616,-80.5687332</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/2807733725</t>
+          <t>https://www.openstreetmap.org/way/965369753</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Cape Crossing Marina</t>
+          <t>Port of the Islands Marina</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -3749,24 +3773,28 @@
       </c>
       <c r="C94" t="inlineStr"/>
       <c r="D94" t="inlineStr"/>
-      <c r="E94" t="inlineStr"/>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>https://portoftheislandsmarina.com/contact-us.html</t>
+        </is>
+      </c>
       <c r="F94" t="inlineStr"/>
       <c r="G94" t="inlineStr"/>
       <c r="H94" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=28.4072204,-80.7072541</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=25.9563367,-81.5107725</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/7029227637</t>
+          <t>https://www.openstreetmap.org/way/1495968632</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Cape Marina</t>
+          <t>Riviera Resort and Marina</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
@@ -3776,32 +3804,32 @@
       </c>
       <c r="C95" t="inlineStr"/>
       <c r="D95" t="inlineStr"/>
-      <c r="E95" t="inlineStr"/>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>http://www.rivieraresort.net/</t>
+        </is>
+      </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>800 Scallop Drive, Cape Canaveral, FL 32920</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>Cape Canaveral</t>
-        </is>
-      </c>
+          <t>2760 Botts Landing Road, 32720</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr"/>
       <c r="H95" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=28.4075422,-80.6274505</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=28.9950347,-81.3673385</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/6558595808</t>
+          <t>https://www.openstreetmap.org/way/158052908</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Captain Hook's Marina &amp; Dive Center</t>
+          <t>Sea Dog Charters Marina</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
@@ -3809,16 +3837,20 @@
           <t>Marina / docks</t>
         </is>
       </c>
-      <c r="C96" t="inlineStr"/>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>(305) 743-8255</t>
+        </is>
+      </c>
       <c r="D96" t="inlineStr"/>
       <c r="E96" t="inlineStr">
         <is>
-          <t>https://captainhooks.com/</t>
+          <t>https://seadogcharters.net</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>11833 Overseas Highway, Marathon, FL 33050</t>
+          <t>1248 Overseas Highway, Marathon, FL 33050</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -3828,19 +3860,19 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=24.7299949,-81.0304125</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=24.7091585,-81.1117446</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/3060410108</t>
+          <t>https://www.openstreetmap.org/node/3060499556</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Captain Hook's Marina and Dive Center</t>
+          <t>Snake Creek Marina</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
@@ -3848,30 +3880,42 @@
           <t>Marina / docks</t>
         </is>
       </c>
-      <c r="C97" t="inlineStr"/>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>(305) 396-7724</t>
+        </is>
+      </c>
       <c r="D97" t="inlineStr"/>
       <c r="E97" t="inlineStr">
         <is>
-          <t>https://captainhooks.com/</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr"/>
-      <c r="G97" t="inlineStr"/>
+          <t>https://snakecreekmarinakeys.com/</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>85401 Overseas Highway, Islamorada, FL 33036</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Islamorada</t>
+        </is>
+      </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=24.7298344,-81.0301698</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=24.9504129,-80.5912068</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/962640922</t>
+          <t>https://www.openstreetmap.org/node/3058696699</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Captiva Landing Marina</t>
+          <t>Snell Isle Marina</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3879,26 +3923,42 @@
           <t>Marina / docks</t>
         </is>
       </c>
-      <c r="C98" t="inlineStr"/>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>(727) 895-8142</t>
+        </is>
+      </c>
       <c r="D98" t="inlineStr"/>
-      <c r="E98" t="inlineStr"/>
-      <c r="F98" t="inlineStr"/>
-      <c r="G98" t="inlineStr"/>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>https://www.spyc.com/</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>1305 Snell Isle Boulevard NE, Saint Petersburg, FL 33704</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Saint Petersburg</t>
+        </is>
+      </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=26.5277351,-82.1896122</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=27.799719,-82.610148</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/1342265268</t>
+          <t>https://www.openstreetmap.org/node/1951987506</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Caribee Boat Sales &amp; Marina</t>
+          <t>Stock Island Yacht Club &amp; Marina</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
@@ -3910,26 +3970,26 @@
       <c r="D99" t="inlineStr"/>
       <c r="E99" t="inlineStr">
         <is>
-          <t>https://www.caribeeboats.com/</t>
+          <t>https://spottswoodmarinas.com/stock-island-yacht-club/</t>
         </is>
       </c>
       <c r="F99" t="inlineStr"/>
       <c r="G99" t="inlineStr"/>
       <c r="H99" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=24.9183449,-80.636662</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=24.5627573,-81.7256669</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/965392909</t>
+          <t>https://www.openstreetmap.org/way/963243452</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Cassen Park Marina</t>
+          <t>Stock Island Yacht Club &amp; Marina - Key West Harbour</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
@@ -3939,24 +3999,28 @@
       </c>
       <c r="C100" t="inlineStr"/>
       <c r="D100" t="inlineStr"/>
-      <c r="E100" t="inlineStr"/>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>https://spottswoodmarinas.com/stock-island-yacht-club/</t>
+        </is>
+      </c>
       <c r="F100" t="inlineStr"/>
       <c r="G100" t="inlineStr"/>
       <c r="H100" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=29.285295,-81.054519</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=24.5639781,-81.727061</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/4733394326</t>
+          <t>https://www.openstreetmap.org/node/3067883937</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Coast Guard Basin</t>
+          <t>Sunset Marina</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
@@ -3966,24 +4030,28 @@
       </c>
       <c r="C101" t="inlineStr"/>
       <c r="D101" t="inlineStr"/>
-      <c r="E101" t="inlineStr"/>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>http://www.sunsetmarinakw.com/</t>
+        </is>
+      </c>
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr"/>
       <c r="H101" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=24.7102583,-81.1063322</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=24.5788844,-81.7504577</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/828589972</t>
+          <t>https://www.openstreetmap.org/way/961607051</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Coconut Point Marina</t>
+          <t>Sunshine Key Marina</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
@@ -3993,24 +4061,28 @@
       </c>
       <c r="C102" t="inlineStr"/>
       <c r="D102" t="inlineStr"/>
-      <c r="E102" t="inlineStr"/>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>http://www.rvonthego.com/florida/sunshine-key-rv-resort-marina/?utm_source=yext&amp;utm_medium=directory&amp;utm_campaign=Yext%20Directory%20Listing</t>
+        </is>
+      </c>
       <c r="F102" t="inlineStr"/>
       <c r="G102" t="inlineStr"/>
       <c r="H102" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=26.3987146,-81.8421983</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=24.6726077,-81.2484539</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/1810734479</t>
+          <t>https://www.openstreetmap.org/way/494903704</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Conch Harbor Marina</t>
+          <t>Telemar Bay Marina</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
@@ -4018,30 +4090,42 @@
           <t>Marina / docks</t>
         </is>
       </c>
-      <c r="C103" t="inlineStr"/>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>(321) 773-2468</t>
+        </is>
+      </c>
       <c r="D103" t="inlineStr"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>https://conchharbormarina.com/</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr"/>
-      <c r="G103" t="inlineStr"/>
+          <t>https://telemarbaymarina.com/</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>1399 Banana River Drive, Indian Harbour Beach, FL 32937</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Indian Harbour Beach</t>
+        </is>
+      </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=24.5628708,-81.8001401</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=28.1492468,-80.6042632</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/960095386</t>
+          <t>https://www.openstreetmap.org/node/9345106335</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Contemporary Marina</t>
+          <t>Uncle Henry's Marina</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
@@ -4049,26 +4133,34 @@
           <t>Marina / docks</t>
         </is>
       </c>
-      <c r="C104" t="inlineStr"/>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>(941) 964-0154</t>
+        </is>
+      </c>
       <c r="D104" t="inlineStr"/>
-      <c r="E104" t="inlineStr"/>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>http://www.unclehenrysmarina.com/</t>
+        </is>
+      </c>
       <c r="F104" t="inlineStr"/>
       <c r="G104" t="inlineStr"/>
       <c r="H104" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=28.415277,-81.5730133</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=26.8032655,-82.2753503</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/344907369</t>
+          <t>https://www.openstreetmap.org/way/964050069</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Coral Bay Marina</t>
+          <t>Walker's Hideaway Marina of Marco Island</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
@@ -4080,26 +4172,26 @@
       <c r="D105" t="inlineStr"/>
       <c r="E105" t="inlineStr">
         <is>
-          <t>https://coral-bay-marina.com/</t>
+          <t>http://www.walkersmarine.com/</t>
         </is>
       </c>
       <c r="F105" t="inlineStr"/>
       <c r="G105" t="inlineStr"/>
       <c r="H105" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=24.9198675,-80.6356235</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=25.9568533,-81.7217535</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/3058734961</t>
+          <t>https://www.openstreetmap.org/node/5482408657</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Cudjoe Gardens Marina And Dive Center</t>
+          <t>Whale Harbor Marina</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
@@ -4109,24 +4201,28 @@
       </c>
       <c r="C106" t="inlineStr"/>
       <c r="D106" t="inlineStr"/>
-      <c r="E106" t="inlineStr"/>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>https://whaleharbormarina.com/</t>
+        </is>
+      </c>
       <c r="F106" t="inlineStr"/>
       <c r="G106" t="inlineStr"/>
       <c r="H106" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=24.6580266,-81.5056317</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=24.9364501,-80.6121534</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/5104474553</t>
+          <t>https://www.openstreetmap.org/node/3058734957</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Davis Islands Yacht Club</t>
+          <t>Adventure Yacht Harbor Marina</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
@@ -4136,36 +4232,24 @@
       </c>
       <c r="C107" t="inlineStr"/>
       <c r="D107" t="inlineStr"/>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>https://www.diyc.org/</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>1315 Severn Avenue, Tampa, FL 33606</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>Tampa</t>
-        </is>
-      </c>
+      <c r="E107" t="inlineStr"/>
+      <c r="F107" t="inlineStr"/>
+      <c r="G107" t="inlineStr"/>
       <c r="H107" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=27.9083573,-82.4499825</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=29.1320088,-80.9618291</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/28937844</t>
+          <t>https://www.openstreetmap.org/way/488741075</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Driftwood Marina &amp; Storage</t>
+          <t>Anclote Village Marina</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
@@ -4176,31 +4260,23 @@
       <c r="C108" t="inlineStr"/>
       <c r="D108" t="inlineStr"/>
       <c r="E108" t="inlineStr"/>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>13900 Overseas Highway, Marathon, 33050</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>Marathon</t>
-        </is>
-      </c>
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="inlineStr"/>
       <c r="H108" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=24.7343614,-81.0121951</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=28.1729981,-82.7856812</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/3060410068</t>
+          <t>https://www.openstreetmap.org/way/1024429087</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Eau Gallie Yacht Basin</t>
+          <t>Bahia Honda Marina</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
@@ -4215,19 +4291,19 @@
       <c r="G109" t="inlineStr"/>
       <c r="H109" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=28.1258262,-80.6274617</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=24.6570071,-81.2783212</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/114585877</t>
+          <t>https://www.openstreetmap.org/way/323507973</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Fisherman's Village Yacht Basin</t>
+          <t>Bay Pines Marina</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
@@ -4242,19 +4318,19 @@
       <c r="G110" t="inlineStr"/>
       <c r="H110" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=26.9293387,-82.0639131</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=27.8153949,-82.765832</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/622927495</t>
+          <t>https://www.openstreetmap.org/node/2346847950</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Flamingo Marina</t>
+          <t>Bayfront Marina (Turtle Beach Marina)</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
@@ -4269,19 +4345,19 @@
       <c r="G111" t="inlineStr"/>
       <c r="H111" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=25.1435513,-80.922796</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=27.2201456,-82.5143547</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/1131832869</t>
+          <t>https://www.openstreetmap.org/node/5930370144</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Florida Bay Marina</t>
+          <t>Boot Key Harbor Marathon City Marina</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
@@ -4296,19 +4372,19 @@
       <c r="G112" t="inlineStr"/>
       <c r="H112" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=25.1418941,-80.9227962</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=24.7097864,-81.091419</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/1131832868</t>
+          <t>https://www.openstreetmap.org/way/589379803</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Florida Sea Base and Brinton Environmental Center</t>
+          <t>Brookside Marina</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
@@ -4323,19 +4399,19 @@
       <c r="G113" t="inlineStr"/>
       <c r="H113" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=24.6619844,-81.4623467</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=26.1395604,-81.77943</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/958732139</t>
+          <t>https://www.openstreetmap.org/way/1537009881</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Foot Hole Marina</t>
+          <t>Burnt Store Marina</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
@@ -4350,19 +4426,19 @@
       <c r="G114" t="inlineStr"/>
       <c r="H114" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=29.7226815,-84.9817982</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=26.7627883,-82.0586868</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/332416418</t>
+          <t>https://www.openstreetmap.org/relation/8721197</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Fort Wilderness Marina</t>
+          <t>Caloosa Yacht &amp; Racquet Club Marina</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4377,19 +4453,19 @@
       <c r="G115" t="inlineStr"/>
       <c r="H115" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=28.4131395,-81.5618635</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=26.5642781,-81.9184075</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/293250542</t>
+          <t>https://www.openstreetmap.org/node/2160330791</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Free Marina Day Slips</t>
+          <t>Calusa Island Marina &amp; Yacht Club</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
@@ -4399,28 +4475,24 @@
       </c>
       <c r="C116" t="inlineStr"/>
       <c r="D116" t="inlineStr"/>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>https://www.sanfordfl.gov/residents/marina-day-slips-1500</t>
-        </is>
-      </c>
+      <c r="E116" t="inlineStr"/>
       <c r="F116" t="inlineStr"/>
       <c r="G116" t="inlineStr"/>
       <c r="H116" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=28.8152803,-81.2677706</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=25.9197202,-81.6514363</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/8934027328</t>
+          <t>https://www.openstreetmap.org/relation/8422119</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Galati Yacht basin</t>
+          <t>Cape Coral Yacht Club</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4435,19 +4507,19 @@
       <c r="G117" t="inlineStr"/>
       <c r="H117" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=27.5266069,-82.721457</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=26.5428428,-81.9514457</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/relation/11488500</t>
+          <t>https://www.openstreetmap.org/node/2807733725</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Galleon Marina</t>
+          <t>Cape Crossing Marina</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
@@ -4457,28 +4529,24 @@
       </c>
       <c r="C118" t="inlineStr"/>
       <c r="D118" t="inlineStr"/>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>https://www.galleonmarinakeywest.com/</t>
-        </is>
-      </c>
+      <c r="E118" t="inlineStr"/>
       <c r="F118" t="inlineStr"/>
       <c r="G118" t="inlineStr"/>
       <c r="H118" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=24.5624049,-81.8029456</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=28.4072204,-80.7072541</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/960077345</t>
+          <t>https://www.openstreetmap.org/node/7029227637</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Grassy Key Marina</t>
+          <t>Cape Marina</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
@@ -4489,23 +4557,31 @@
       <c r="C119" t="inlineStr"/>
       <c r="D119" t="inlineStr"/>
       <c r="E119" t="inlineStr"/>
-      <c r="F119" t="inlineStr"/>
-      <c r="G119" t="inlineStr"/>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>800 Scallop Drive, Cape Canaveral, FL 32920</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Cape Canaveral</t>
+        </is>
+      </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=24.7684309,-80.9443875</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=28.4075422,-80.6274505</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/3060410048</t>
+          <t>https://www.openstreetmap.org/node/6558595808</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Gulfport Municipal Marina</t>
+          <t>Captiva Landing Marina</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
@@ -4516,31 +4592,23 @@
       <c r="C120" t="inlineStr"/>
       <c r="D120" t="inlineStr"/>
       <c r="E120" t="inlineStr"/>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>Gulfport, FL 33711</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>Gulfport</t>
-        </is>
-      </c>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="inlineStr"/>
       <c r="H120" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=27.7400103,-82.6958172</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=26.5277351,-82.1896122</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/588188174</t>
+          <t>https://www.openstreetmap.org/way/1342265268</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Halifax Harbor Marina</t>
+          <t>Cassen Park Marina</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
@@ -4555,19 +4623,19 @@
       <c r="G121" t="inlineStr"/>
       <c r="H121" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=29.2041299,-81.0125605</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=29.285295,-81.054519</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/6685567336</t>
+          <t>https://www.openstreetmap.org/node/4733394326</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Harbor Marina</t>
+          <t>Coast Guard Basin</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
@@ -4582,19 +4650,19 @@
       <c r="G122" t="inlineStr"/>
       <c r="H122" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=27.9670792,-82.8047447</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=24.7102583,-81.1063322</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/1461782610</t>
+          <t>https://www.openstreetmap.org/way/828589972</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Harborage Marina</t>
+          <t>Coconut Point Marina</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
@@ -4605,31 +4673,23 @@
       <c r="C123" t="inlineStr"/>
       <c r="D123" t="inlineStr"/>
       <c r="E123" t="inlineStr"/>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>Saint Petersburg, FL 33712;33701</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>Saint Petersburg</t>
-        </is>
-      </c>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr"/>
       <c r="H123" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=27.7598297,-82.6353792</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=26.3987146,-81.8421983</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/1463793070</t>
+          <t>https://www.openstreetmap.org/node/1810734479</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Harbour Village Marina</t>
+          <t>Contemporary Marina</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
@@ -4644,19 +4704,19 @@
       <c r="G124" t="inlineStr"/>
       <c r="H124" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=29.10175,-80.9470981</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=28.415277,-81.5730133</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/488742478</t>
+          <t>https://www.openstreetmap.org/way/344907369</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Hawks Cay Resort Marina</t>
+          <t>Cudjoe Gardens Marina And Dive Center</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
@@ -4666,28 +4726,24 @@
       </c>
       <c r="C125" t="inlineStr"/>
       <c r="D125" t="inlineStr"/>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>https://www.hawkscay.com/amenities/hawks-cay-marina</t>
-        </is>
-      </c>
+      <c r="E125" t="inlineStr"/>
       <c r="F125" t="inlineStr"/>
       <c r="G125" t="inlineStr"/>
       <c r="H125" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=24.7779182,-80.9131337</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=24.6580266,-81.5056317</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/8922857152</t>
+          <t>https://www.openstreetmap.org/node/5104474553</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Hernando Beach Marina</t>
+          <t>Driftwood Marina &amp; Storage</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
@@ -4700,25 +4756,29 @@
       <c r="E126" t="inlineStr"/>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Shoal Line Blvd, FL 34607</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr"/>
+          <t>13900 Overseas Highway, Marathon, 33050</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Marathon</t>
+        </is>
+      </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=28.4900884,-82.6507817</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=24.7343614,-81.0121951</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/1253508548</t>
+          <t>https://www.openstreetmap.org/node/3060410068</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Home Port Marina</t>
+          <t>Eau Gallie Yacht Basin</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
@@ -4733,19 +4793,19 @@
       <c r="G127" t="inlineStr"/>
       <c r="H127" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=28.0596234,-82.7768397</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=28.1258262,-80.6274617</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/773868275</t>
+          <t>https://www.openstreetmap.org/way/114585877</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Hubbards Marina</t>
+          <t>Fisherman's Village Yacht Basin</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
@@ -4760,19 +4820,19 @@
       <c r="G128" t="inlineStr"/>
       <c r="H128" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=27.7846277,-82.7823164</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=26.9293387,-82.0639131</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/231594757</t>
+          <t>https://www.openstreetmap.org/way/622927495</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Hurricane Hole Marina</t>
+          <t>Flamingo Marina</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
@@ -4787,19 +4847,19 @@
       <c r="G129" t="inlineStr"/>
       <c r="H129" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=24.5709967,-81.747301</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=25.1435513,-80.922796</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/3060595253</t>
+          <t>https://www.openstreetmap.org/way/1131832869</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Inlet Harbor Marina</t>
+          <t>Florida Bay Marina</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
@@ -4814,19 +4874,19 @@
       <c r="G130" t="inlineStr"/>
       <c r="H130" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=29.0916495,-80.9387579</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=25.1418941,-80.9227962</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/399299551</t>
+          <t>https://www.openstreetmap.org/way/1131832868</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>IslaMarina</t>
+          <t>Florida Sea Base and Brinton Environmental Center</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
@@ -4836,28 +4896,24 @@
       </c>
       <c r="C131" t="inlineStr"/>
       <c r="D131" t="inlineStr"/>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>https://islamarinakeys.com/</t>
-        </is>
-      </c>
+      <c r="E131" t="inlineStr"/>
       <c r="F131" t="inlineStr"/>
       <c r="G131" t="inlineStr"/>
       <c r="H131" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=24.9535923,-80.5855417</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=24.6619844,-81.4623467</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/965374081</t>
+          <t>https://www.openstreetmap.org/way/958732139</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Isles Yacht Club</t>
+          <t>Foot Hole Marina</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
@@ -4872,19 +4928,19 @@
       <c r="G132" t="inlineStr"/>
       <c r="H132" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=26.9246379,-82.0723239</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=29.7226815,-84.9817982</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/1821778067</t>
+          <t>https://www.openstreetmap.org/way/332416418</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Key West Bight Marina</t>
+          <t>Fort Wilderness Marina</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
@@ -4894,28 +4950,24 @@
       </c>
       <c r="C133" t="inlineStr"/>
       <c r="D133" t="inlineStr"/>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>https://www.keywestbightmarina.com/</t>
-        </is>
-      </c>
+      <c r="E133" t="inlineStr"/>
       <c r="F133" t="inlineStr"/>
       <c r="G133" t="inlineStr"/>
       <c r="H133" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=24.5619147,-81.8016413</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=28.4131395,-81.5618635</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/83579780</t>
+          <t>https://www.openstreetmap.org/way/293250542</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Laishley Marina</t>
+          <t>Galati Yacht basin</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
@@ -4930,19 +4982,19 @@
       <c r="G134" t="inlineStr"/>
       <c r="H134" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=26.9394607,-82.0515501</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=27.5266069,-82.721457</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/1666521165</t>
+          <t>https://www.openstreetmap.org/relation/11488500</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Lake Fairview Marina</t>
+          <t>Grassy Key Marina</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
@@ -4957,19 +5009,19 @@
       <c r="G135" t="inlineStr"/>
       <c r="H135" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=28.595929,-81.414855</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=24.7684309,-80.9443875</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/933955759</t>
+          <t>https://www.openstreetmap.org/node/3060410048</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Lakeshore Marina</t>
+          <t>Gulfport Municipal Marina</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
@@ -4980,23 +5032,31 @@
       <c r="C136" t="inlineStr"/>
       <c r="D136" t="inlineStr"/>
       <c r="E136" t="inlineStr"/>
-      <c r="F136" t="inlineStr"/>
-      <c r="G136" t="inlineStr"/>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Gulfport, FL 33711</t>
+        </is>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>Gulfport</t>
+        </is>
+      </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=27.8545536,-81.4114386</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=27.7400103,-82.6958172</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/1704093768</t>
+          <t>https://www.openstreetmap.org/node/588188174</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Lighthouse Boatyard</t>
+          <t>Halifax Harbor Marina</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -5011,19 +5071,19 @@
       <c r="G137" t="inlineStr"/>
       <c r="H137" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=29.0791517,-80.9272674</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=29.2041299,-81.0125605</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/399304728</t>
+          <t>https://www.openstreetmap.org/node/6685567336</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Lighthouse Point Marina</t>
+          <t>Harbor Marina</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -5038,19 +5098,19 @@
       <c r="G138" t="inlineStr"/>
       <c r="H138" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=27.8118553,-82.7598111</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=27.9670792,-82.8047447</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/4184366922</t>
+          <t>https://www.openstreetmap.org/way/1461782610</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Little Harbor Marina</t>
+          <t>Harborage Marina</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -5061,23 +5121,31 @@
       <c r="C139" t="inlineStr"/>
       <c r="D139" t="inlineStr"/>
       <c r="E139" t="inlineStr"/>
-      <c r="F139" t="inlineStr"/>
-      <c r="G139" t="inlineStr"/>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Saint Petersburg, FL 33712;33701</t>
+        </is>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>Saint Petersburg</t>
+        </is>
+      </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=27.7252832,-82.4698544</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=27.7598297,-82.6353792</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/7157067330</t>
+          <t>https://www.openstreetmap.org/way/1463793070</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Madeira Beach Municipal Marina</t>
+          <t>Harbour Village Marina</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -5092,19 +5160,19 @@
       <c r="G140" t="inlineStr"/>
       <c r="H140" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=27.8039736,-82.7959026</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=29.10175,-80.9470981</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/2346797222</t>
+          <t>https://www.openstreetmap.org/way/488742478</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Marathon Marina &amp; Boat Yard</t>
+          <t>Hernando Beach Marina</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -5114,28 +5182,28 @@
       </c>
       <c r="C141" t="inlineStr"/>
       <c r="D141" t="inlineStr"/>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>https://marathonmarinaresort.com</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr"/>
+      <c r="E141" t="inlineStr"/>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Shoal Line Blvd, FL 34607</t>
+        </is>
+      </c>
       <c r="G141" t="inlineStr"/>
       <c r="H141" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=24.7046204,-81.1121887</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=28.4900884,-82.6507817</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/962279125</t>
+          <t>https://www.openstreetmap.org/way/1253508548</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Marco Island Marina</t>
+          <t>Home Port Marina</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -5150,19 +5218,19 @@
       <c r="G142" t="inlineStr"/>
       <c r="H142" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=25.9609741,-81.712715</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=28.0596234,-82.7768397</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/494897410</t>
+          <t>https://www.openstreetmap.org/way/773868275</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Marina</t>
+          <t>Hubbards Marina</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -5177,19 +5245,19 @@
       <c r="G143" t="inlineStr"/>
       <c r="H143" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=29.7640511,-85.4022291</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=27.7846277,-82.7823164</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/333319325</t>
+          <t>https://www.openstreetmap.org/way/231594757</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Marina @ Bayshore Gardens</t>
+          <t>Hurricane Hole Marina</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -5200,31 +5268,23 @@
       <c r="C144" t="inlineStr"/>
       <c r="D144" t="inlineStr"/>
       <c r="E144" t="inlineStr"/>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>6919 26th Street West, Bradenton, FL 34207</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>Bradenton</t>
-        </is>
-      </c>
+      <c r="F144" t="inlineStr"/>
+      <c r="G144" t="inlineStr"/>
       <c r="H144" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=27.4202866,-82.585908</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=24.5709967,-81.747301</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/493012663</t>
+          <t>https://www.openstreetmap.org/node/3060595253</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Marina del Palma</t>
+          <t>Inlet Harbor Marina</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -5239,19 +5299,19 @@
       <c r="G145" t="inlineStr"/>
       <c r="H145" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=29.497423,-81.1500249</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=29.0916495,-80.9387579</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/1387648325</t>
+          <t>https://www.openstreetmap.org/way/399299551</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Marineland Marina</t>
+          <t>Isles Yacht Club</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -5266,19 +5326,19 @@
       <c r="G146" t="inlineStr"/>
       <c r="H146" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=29.6691195,-81.2150376</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=26.9246379,-82.0723239</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/333629430</t>
+          <t>https://www.openstreetmap.org/node/1821778067</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Marjorie Park Marina</t>
+          <t>Laishley Marina</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -5293,19 +5353,19 @@
       <c r="G147" t="inlineStr"/>
       <c r="H147" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=27.9307781,-82.4541047</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=26.9394607,-82.0515501</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/1463801814</t>
+          <t>https://www.openstreetmap.org/node/1666521165</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Marker 1 Marina</t>
+          <t>Lake Fairview Marina</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -5316,27 +5376,23 @@
       <c r="C148" t="inlineStr"/>
       <c r="D148" t="inlineStr"/>
       <c r="E148" t="inlineStr"/>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>Causeway Blvd, FL 34698</t>
-        </is>
-      </c>
+      <c r="F148" t="inlineStr"/>
       <c r="G148" t="inlineStr"/>
       <c r="H148" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=28.0503864,-82.7863152</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=28.595929,-81.414855</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/1948059616</t>
+          <t>https://www.openstreetmap.org/way/933955759</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Maximo Marina - Saint Petersburg/Tampa</t>
+          <t>Lakeshore Marina</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -5346,28 +5402,24 @@
       </c>
       <c r="C149" t="inlineStr"/>
       <c r="D149" t="inlineStr"/>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>http://www.igy-maximomarina.com/</t>
-        </is>
-      </c>
+      <c r="E149" t="inlineStr"/>
       <c r="F149" t="inlineStr"/>
       <c r="G149" t="inlineStr"/>
       <c r="H149" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=27.7243732,-82.6823903</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=27.8545536,-81.4114386</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/609719332</t>
+          <t>https://www.openstreetmap.org/node/1704093768</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Monroe Harbour Marina</t>
+          <t>Lighthouse Boatyard</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -5377,28 +5429,24 @@
       </c>
       <c r="C150" t="inlineStr"/>
       <c r="D150" t="inlineStr"/>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>http://www.monroeharbour.com/</t>
-        </is>
-      </c>
+      <c r="E150" t="inlineStr"/>
       <c r="F150" t="inlineStr"/>
       <c r="G150" t="inlineStr"/>
       <c r="H150" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=28.8150946,-81.2668498</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=29.0791517,-80.9272674</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/964718295</t>
+          <t>https://www.openstreetmap.org/way/399304728</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Mullock Creek Marina</t>
+          <t>Lighthouse Point Marina</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -5413,19 +5461,19 @@
       <c r="G151" t="inlineStr"/>
       <c r="H151" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=26.4734951,-81.8513687</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=27.8118553,-82.7598111</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/1928488392</t>
+          <t>https://www.openstreetmap.org/node/4184366922</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Municipal Marina</t>
+          <t>Little Harbor Marina</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -5435,28 +5483,24 @@
       </c>
       <c r="C152" t="inlineStr"/>
       <c r="D152" t="inlineStr"/>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>https://www.dunedingov.com/index.aspx?page=151</t>
-        </is>
-      </c>
+      <c r="E152" t="inlineStr"/>
       <c r="F152" t="inlineStr"/>
       <c r="G152" t="inlineStr"/>
       <c r="H152" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=28.0124558,-82.7922848</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=27.7252832,-82.4698544</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/523224923</t>
+          <t>https://www.openstreetmap.org/node/7157067330</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Murray Marine</t>
+          <t>Madeira Beach Municipal Marina</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -5467,31 +5511,23 @@
       <c r="C153" t="inlineStr"/>
       <c r="D153" t="inlineStr"/>
       <c r="E153" t="inlineStr"/>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>5710 Overseas Highway, Key West, 33040</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>Key West</t>
-        </is>
-      </c>
+      <c r="F153" t="inlineStr"/>
+      <c r="G153" t="inlineStr"/>
       <c r="H153" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=24.5743233,-81.7355179</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=27.8039736,-82.7959026</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/3060595241</t>
+          <t>https://www.openstreetmap.org/node/2346797222</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Naples Boat Club</t>
+          <t>Marco Island Marina</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -5506,19 +5542,19 @@
       <c r="G154" t="inlineStr"/>
       <c r="H154" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=26.1379145,-81.7910926</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=25.9609741,-81.712715</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/1351010688</t>
+          <t>https://www.openstreetmap.org/way/494897410</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Naples City Dock</t>
+          <t>Marina</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -5533,19 +5569,19 @@
       <c r="G155" t="inlineStr"/>
       <c r="H155" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=26.1322842,-81.7932941</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=29.7640511,-85.4022291</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/1341692593</t>
+          <t>https://www.openstreetmap.org/way/333319325</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Naples Sailing &amp; Yacht Club</t>
+          <t>Marina @ Bayshore Gardens</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -5556,23 +5592,31 @@
       <c r="C156" t="inlineStr"/>
       <c r="D156" t="inlineStr"/>
       <c r="E156" t="inlineStr"/>
-      <c r="F156" t="inlineStr"/>
-      <c r="G156" t="inlineStr"/>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>6919 26th Street West, Bradenton, FL 34207</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>Bradenton</t>
+        </is>
+      </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=26.1379633,-81.7888299</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=27.4202866,-82.585908</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/702316224</t>
+          <t>https://www.openstreetmap.org/way/493012663</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Naples Yacht Club</t>
+          <t>Marina del Palma</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -5587,19 +5631,19 @@
       <c r="G157" t="inlineStr"/>
       <c r="H157" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=26.1304273,-81.7944015</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=29.497423,-81.1500249</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/1341693160</t>
+          <t>https://www.openstreetmap.org/way/1387648325</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Nature Coast Marina</t>
+          <t>Marineland Marina</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -5614,19 +5658,19 @@
       <c r="G158" t="inlineStr"/>
       <c r="H158" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=28.4907427,-82.6508412</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=29.6691195,-81.2150376</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/1253510074</t>
+          <t>https://www.openstreetmap.org/way/333629430</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Nav-A-Gator Marina</t>
+          <t>Marjorie Park Marina</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -5641,19 +5685,19 @@
       <c r="G159" t="inlineStr"/>
       <c r="H159" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=27.0612458,-82.002513</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=27.9307781,-82.4541047</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/1666444764</t>
+          <t>https://www.openstreetmap.org/way/1463801814</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>New Smyrna Marina</t>
+          <t>Marker 1 Marina</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -5664,23 +5708,27 @@
       <c r="C160" t="inlineStr"/>
       <c r="D160" t="inlineStr"/>
       <c r="E160" t="inlineStr"/>
-      <c r="F160" t="inlineStr"/>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Causeway Blvd, FL 34698</t>
+        </is>
+      </c>
       <c r="G160" t="inlineStr"/>
       <c r="H160" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=29.0321076,-80.9136961</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=28.0503864,-82.7863152</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/489168014</t>
+          <t>https://www.openstreetmap.org/node/1948059616</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Oasis Marina</t>
+          <t>Mullock Creek Marina</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -5690,28 +5738,24 @@
       </c>
       <c r="C161" t="inlineStr"/>
       <c r="D161" t="inlineStr"/>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>https://www.oasismarinas.com/</t>
-        </is>
-      </c>
+      <c r="E161" t="inlineStr"/>
       <c r="F161" t="inlineStr"/>
       <c r="G161" t="inlineStr"/>
       <c r="H161" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=24.5643553,-81.7375146</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=26.4734951,-81.8513687</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/relation/15741992</t>
+          <t>https://www.openstreetmap.org/node/1928488392</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Oceans Edge Resort &amp; Marina Key West</t>
+          <t>Murray Marine</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -5721,14 +5765,10 @@
       </c>
       <c r="C162" t="inlineStr"/>
       <c r="D162" t="inlineStr"/>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>https://www.oceansedgekeywest.com/</t>
-        </is>
-      </c>
+      <c r="E162" t="inlineStr"/>
       <c r="F162" t="inlineStr">
         <is>
-          <t>5950 Peninsular Avenue, Key West, FL 33040</t>
+          <t>5710 Overseas Highway, Key West, 33040</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
@@ -5738,19 +5778,19 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=24.5631903,-81.7298505</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=24.5743233,-81.7355179</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/415309284</t>
+          <t>https://www.openstreetmap.org/node/3060595241</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Old Wooden Bridge Guest Cottages &amp; Marina LLC</t>
+          <t>Naples Boat Club</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -5765,19 +5805,19 @@
       <c r="G163" t="inlineStr"/>
       <c r="H163" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=24.6971725,-81.3482461</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=26.1379145,-81.7910926</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/493483962</t>
+          <t>https://www.openstreetmap.org/way/1351010688</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Olde Naples Seaport</t>
+          <t>Naples City Dock</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -5792,19 +5832,19 @@
       <c r="G164" t="inlineStr"/>
       <c r="H164" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=26.1369364,-81.7908149</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=26.1322842,-81.7932941</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/1351010687</t>
+          <t>https://www.openstreetmap.org/way/1341692593</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Palm Coast Marina</t>
+          <t>Naples Sailing &amp; Yacht Club</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -5819,19 +5859,19 @@
       <c r="G165" t="inlineStr"/>
       <c r="H165" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=29.5768693,-81.19332</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=26.1379633,-81.7888299</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/1346449745</t>
+          <t>https://www.openstreetmap.org/way/702316224</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Paradise Marina</t>
+          <t>Naples Yacht Club</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -5842,31 +5882,23 @@
       <c r="C166" t="inlineStr"/>
       <c r="D166" t="inlineStr"/>
       <c r="E166" t="inlineStr"/>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>3900 Orange Grove Boulevard, Cape Coral, FL 33909</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>Cape Coral</t>
-        </is>
-      </c>
+      <c r="F166" t="inlineStr"/>
+      <c r="G166" t="inlineStr"/>
       <c r="H166" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=26.6284878,-81.9172576</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=26.1304273,-81.7944015</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/324084294</t>
+          <t>https://www.openstreetmap.org/way/1341693160</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Park Shore Marina</t>
+          <t>Nature Coast Marina</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -5881,19 +5913,19 @@
       <c r="G167" t="inlineStr"/>
       <c r="H167" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=26.197937,-81.8123155</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=28.4907427,-82.6508412</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/7120744951</t>
+          <t>https://www.openstreetmap.org/way/1253510074</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Pete's Pier Marina</t>
+          <t>Nav-A-Gator Marina</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -5903,28 +5935,24 @@
       </c>
       <c r="C168" t="inlineStr"/>
       <c r="D168" t="inlineStr"/>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>https://www.petespier.com</t>
-        </is>
-      </c>
+      <c r="E168" t="inlineStr"/>
       <c r="F168" t="inlineStr"/>
       <c r="G168" t="inlineStr"/>
       <c r="H168" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=28.8948545,-82.597468</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=27.0612458,-82.002513</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/11813178785</t>
+          <t>https://www.openstreetmap.org/node/1666444764</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Pineland Marina</t>
+          <t>New Smyrna Marina</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -5939,19 +5967,19 @@
       <c r="G169" t="inlineStr"/>
       <c r="H169" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=26.6627372,-82.1535357</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=29.0321076,-80.9136961</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/180717971</t>
+          <t>https://www.openstreetmap.org/way/489168014</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Piper's Marine</t>
+          <t>Old Wooden Bridge Guest Cottages &amp; Marina LLC</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -5962,31 +5990,23 @@
       <c r="C170" t="inlineStr"/>
       <c r="D170" t="inlineStr"/>
       <c r="E170" t="inlineStr"/>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>Rocky Creek Dr, Tampa, FL 33615</t>
-        </is>
-      </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>Tampa</t>
-        </is>
-      </c>
+      <c r="F170" t="inlineStr"/>
+      <c r="G170" t="inlineStr"/>
       <c r="H170" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=27.996723,-82.5863879</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=24.6971725,-81.3482461</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/1834811276</t>
+          <t>https://www.openstreetmap.org/way/493483962</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Plantation Yacht Harbor Marina</t>
+          <t>Olde Naples Seaport</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -5996,28 +6016,24 @@
       </c>
       <c r="C171" t="inlineStr"/>
       <c r="D171" t="inlineStr"/>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>https://www.islamorada.fl.us/</t>
-        </is>
-      </c>
+      <c r="E171" t="inlineStr"/>
       <c r="F171" t="inlineStr"/>
       <c r="G171" t="inlineStr"/>
       <c r="H171" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=24.9648616,-80.5687332</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=26.1369364,-81.7908149</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/965369753</t>
+          <t>https://www.openstreetmap.org/way/1351010687</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Pointe Marina</t>
+          <t>Palm Coast Marina</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -6032,19 +6048,19 @@
       <c r="G172" t="inlineStr"/>
       <c r="H172" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=27.9393175,-82.4546185</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=29.5768693,-81.19332</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/10670157340</t>
+          <t>https://www.openstreetmap.org/way/1346449745</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Port of the Islands Marina</t>
+          <t>Paradise Marina</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -6054,28 +6070,32 @@
       </c>
       <c r="C173" t="inlineStr"/>
       <c r="D173" t="inlineStr"/>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>https://portoftheislandsmarina.com/contact-us.html</t>
-        </is>
-      </c>
-      <c r="F173" t="inlineStr"/>
-      <c r="G173" t="inlineStr"/>
+      <c r="E173" t="inlineStr"/>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>3900 Orange Grove Boulevard, Cape Coral, FL 33909</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>Cape Coral</t>
+        </is>
+      </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=25.9563367,-81.5107725</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=26.6284878,-81.9172576</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/1495968632</t>
+          <t>https://www.openstreetmap.org/way/324084294</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Regatta Pointe Marina</t>
+          <t>Park Shore Marina</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -6090,19 +6110,19 @@
       <c r="G174" t="inlineStr"/>
       <c r="H174" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=27.5099673,-82.5756067</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=26.197937,-81.8123155</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/495984054</t>
+          <t>https://www.openstreetmap.org/node/7120744951</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Riverhaven</t>
+          <t>Pineland Marina</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -6117,19 +6137,19 @@
       <c r="G175" t="inlineStr"/>
       <c r="H175" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=28.7852478,-82.6209689</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=26.6627372,-82.1535357</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/149509334</t>
+          <t>https://www.openstreetmap.org/way/180717971</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Riverhaven Marina</t>
+          <t>Piper's Marine</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -6142,25 +6162,29 @@
       <c r="E176" t="inlineStr"/>
       <c r="F176" t="inlineStr">
         <is>
-          <t>S Riverview Cir, FL 34448</t>
-        </is>
-      </c>
-      <c r="G176" t="inlineStr"/>
+          <t>Rocky Creek Dr, Tampa, FL 33615</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>Tampa</t>
+        </is>
+      </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=28.7851964,-82.6209702</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=27.996723,-82.5863879</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/1884089288</t>
+          <t>https://www.openstreetmap.org/node/1834811276</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Riviera Marina</t>
+          <t>Pointe Marina</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -6175,19 +6199,19 @@
       <c r="G177" t="inlineStr"/>
       <c r="H177" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=26.8886769,-82.05372</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=27.9393175,-82.4546185</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/628714067</t>
+          <t>https://www.openstreetmap.org/node/10670157340</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Riviera Resort and Marina</t>
+          <t>Regatta Pointe Marina</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -6197,32 +6221,24 @@
       </c>
       <c r="C178" t="inlineStr"/>
       <c r="D178" t="inlineStr"/>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>http://www.rivieraresort.net/</t>
-        </is>
-      </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>2760 Botts Landing Road, 32720</t>
-        </is>
-      </c>
+      <c r="E178" t="inlineStr"/>
+      <c r="F178" t="inlineStr"/>
       <c r="G178" t="inlineStr"/>
       <c r="H178" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=28.9950347,-81.3673385</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=27.5099673,-82.5756067</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/158052908</t>
+          <t>https://www.openstreetmap.org/way/495984054</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Robbie's</t>
+          <t>Riverhaven</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -6233,31 +6249,23 @@
       <c r="C179" t="inlineStr"/>
       <c r="D179" t="inlineStr"/>
       <c r="E179" t="inlineStr"/>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>77522 Overseas Highway, Islamorada, 33036</t>
-        </is>
-      </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>Islamorada</t>
-        </is>
-      </c>
+      <c r="F179" t="inlineStr"/>
+      <c r="G179" t="inlineStr"/>
       <c r="H179" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=24.8827405,-80.6907395</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=28.7852478,-82.6209689</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/3058878543</t>
+          <t>https://www.openstreetmap.org/way/149509334</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Safety Harbor Marina</t>
+          <t>Riverhaven Marina</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -6270,29 +6278,25 @@
       <c r="E180" t="inlineStr"/>
       <c r="F180" t="inlineStr">
         <is>
-          <t>Veterans Memorial Ln, Safety Harbor, FL 34695</t>
-        </is>
-      </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>Safety Harbor</t>
-        </is>
-      </c>
+          <t>S Riverview Cir, FL 34448</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr"/>
       <c r="H180" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=27.9892669,-82.6874995</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=28.7851964,-82.6209702</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/1768178168</t>
+          <t>https://www.openstreetmap.org/node/1884089288</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Santina Marina Plaza</t>
+          <t>Riviera Marina</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -6307,19 +6311,19 @@
       <c r="G181" t="inlineStr"/>
       <c r="H181" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=26.4136773,-81.8992028</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=26.8886769,-82.05372</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/613014422</t>
+          <t>https://www.openstreetmap.org/way/628714067</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Scouts BSA Florida Sea Base</t>
+          <t>Robbie's</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -6332,7 +6336,7 @@
       <c r="E182" t="inlineStr"/>
       <c r="F182" t="inlineStr">
         <is>
-          <t>73800 Overseas Highway, Islamorada, FL 33036</t>
+          <t>77522 Overseas Highway, Islamorada, 33036</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
@@ -6342,19 +6346,19 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=24.8513324,-80.7377656</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=24.8827405,-80.6907395</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/3358983501</t>
+          <t>https://www.openstreetmap.org/node/3058878543</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Sea Bird Marina</t>
+          <t>Safety Harbor Marina</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -6367,29 +6371,29 @@
       <c r="E183" t="inlineStr"/>
       <c r="F183" t="inlineStr">
         <is>
-          <t>69501 Overseas Highway, Layton, 33001</t>
+          <t>Veterans Memorial Ln, Safety Harbor, FL 34695</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Layton</t>
+          <t>Safety Harbor</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=24.8378436,-80.7988319</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=27.9892669,-82.6874995</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/3058878550</t>
+          <t>https://www.openstreetmap.org/node/1768178168</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Sea Love Marina</t>
+          <t>Santina Marina Plaza</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -6404,19 +6408,19 @@
       <c r="G184" t="inlineStr"/>
       <c r="H184" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=29.0823409,-80.9351178</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=26.4136773,-81.8992028</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/399302391</t>
+          <t>https://www.openstreetmap.org/way/613014422</t>
         </is>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>Shell Point Marina</t>
+          <t>Scouts BSA Florida Sea Base</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -6427,23 +6431,31 @@
       <c r="C185" t="inlineStr"/>
       <c r="D185" t="inlineStr"/>
       <c r="E185" t="inlineStr"/>
-      <c r="F185" t="inlineStr"/>
-      <c r="G185" t="inlineStr"/>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>73800 Overseas Highway, Islamorada, FL 33036</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>Islamorada</t>
+        </is>
+      </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=26.5169042,-81.9991945</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=24.8513324,-80.7377656</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/177480246</t>
+          <t>https://www.openstreetmap.org/node/3358983501</t>
         </is>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>SpaceX Barge Dock</t>
+          <t>Sea Bird Marina</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -6454,23 +6466,31 @@
       <c r="C186" t="inlineStr"/>
       <c r="D186" t="inlineStr"/>
       <c r="E186" t="inlineStr"/>
-      <c r="F186" t="inlineStr"/>
-      <c r="G186" t="inlineStr"/>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>69501 Overseas Highway, Layton, 33001</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
+          <t>Layton</t>
+        </is>
+      </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=28.4170103,-80.6239972</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=24.8378436,-80.7988319</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/4202762203</t>
+          <t>https://www.openstreetmap.org/node/3058878550</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>Spirit Snorkeling</t>
+          <t>Sea Love Marina</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -6481,31 +6501,23 @@
       <c r="C187" t="inlineStr"/>
       <c r="D187" t="inlineStr"/>
       <c r="E187" t="inlineStr"/>
-      <c r="F187" t="inlineStr">
-        <is>
-          <t>1400 Overseas Highway, Marathon, 33050</t>
-        </is>
-      </c>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>Marathon</t>
-        </is>
-      </c>
+      <c r="F187" t="inlineStr"/>
+      <c r="G187" t="inlineStr"/>
       <c r="H187" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=24.7085536,-81.1103322</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=29.0823409,-80.9351178</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/3067857966</t>
+          <t>https://www.openstreetmap.org/way/399302391</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>St Petersburg Municipal Marina</t>
+          <t>Shell Point Marina</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -6520,19 +6532,19 @@
       <c r="G188" t="inlineStr"/>
       <c r="H188" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=27.7704574,-82.629037</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=26.5169042,-81.9991945</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/relation/20041419</t>
+          <t>https://www.openstreetmap.org/way/177480246</t>
         </is>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>St Petersburg Sailing Center</t>
+          <t>SpaceX Barge Dock</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -6543,31 +6555,23 @@
       <c r="C189" t="inlineStr"/>
       <c r="D189" t="inlineStr"/>
       <c r="E189" t="inlineStr"/>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t>250 2nd Avenue Southeast, St Petersburg, FL 33701</t>
-        </is>
-      </c>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>St Petersburg</t>
-        </is>
-      </c>
+      <c r="F189" t="inlineStr"/>
+      <c r="G189" t="inlineStr"/>
       <c r="H189" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=27.7694894,-82.631504</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=28.4170103,-80.6239972</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/1463793048</t>
+          <t>https://www.openstreetmap.org/node/4202762203</t>
         </is>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>St Petersburg Yacht Club - Downtown Marina</t>
+          <t>Spirit Snorkeling</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -6580,29 +6584,29 @@
       <c r="E190" t="inlineStr"/>
       <c r="F190" t="inlineStr">
         <is>
-          <t>50 Bay Shore Drive Northeast, Saint Petersburg, FL 33701</t>
+          <t>1400 Overseas Highway, Marathon, 33050</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>Saint Petersburg</t>
+          <t>Marathon</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=27.7715315,-82.631746</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=24.7085536,-81.1103322</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/1463793061</t>
+          <t>https://www.openstreetmap.org/node/3067857966</t>
         </is>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>St. Petersburg Municipal Marina</t>
+          <t>St Petersburg Sailing Center</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -6613,23 +6617,31 @@
       <c r="C191" t="inlineStr"/>
       <c r="D191" t="inlineStr"/>
       <c r="E191" t="inlineStr"/>
-      <c r="F191" t="inlineStr"/>
-      <c r="G191" t="inlineStr"/>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>250 2nd Avenue Southeast, St Petersburg, FL 33701</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>St Petersburg</t>
+        </is>
+      </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=27.7717283,-82.6279038</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=27.7694894,-82.631504</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/226879742</t>
+          <t>https://www.openstreetmap.org/way/1463793048</t>
         </is>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>Starfish Snorkel</t>
+          <t>St Petersburg Yacht Club - Downtown Marina</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -6640,23 +6652,31 @@
       <c r="C192" t="inlineStr"/>
       <c r="D192" t="inlineStr"/>
       <c r="E192" t="inlineStr"/>
-      <c r="F192" t="inlineStr"/>
-      <c r="G192" t="inlineStr"/>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>50 Bay Shore Drive Northeast, Saint Petersburg, FL 33701</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
+        <is>
+          <t>Saint Petersburg</t>
+        </is>
+      </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=24.7085298,-81.1115461</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=27.7715315,-82.631746</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/3060499557</t>
+          <t>https://www.openstreetmap.org/way/1463793061</t>
         </is>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>Sterling Marina</t>
+          <t>St. Petersburg Municipal Marina</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -6671,19 +6691,19 @@
       <c r="G193" t="inlineStr"/>
       <c r="H193" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=28.4918618,-82.6504993</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=27.7717283,-82.6279038</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/1253511889</t>
+          <t>https://www.openstreetmap.org/way/226879742</t>
         </is>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>Stock Island Yacht Club &amp; Marina</t>
+          <t>Starfish Snorkel</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -6693,28 +6713,24 @@
       </c>
       <c r="C194" t="inlineStr"/>
       <c r="D194" t="inlineStr"/>
-      <c r="E194" t="inlineStr">
-        <is>
-          <t>https://spottswoodmarinas.com/stock-island-yacht-club/</t>
-        </is>
-      </c>
+      <c r="E194" t="inlineStr"/>
       <c r="F194" t="inlineStr"/>
       <c r="G194" t="inlineStr"/>
       <c r="H194" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=24.5627573,-81.7256669</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=24.7085298,-81.1115461</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/963243452</t>
+          <t>https://www.openstreetmap.org/node/3060499557</t>
         </is>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>Stock Island Yacht Club &amp; Marina - Key West Harbour</t>
+          <t>Sterling Marina</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -6724,28 +6740,24 @@
       </c>
       <c r="C195" t="inlineStr"/>
       <c r="D195" t="inlineStr"/>
-      <c r="E195" t="inlineStr">
-        <is>
-          <t>https://spottswoodmarinas.com/stock-island-yacht-club/</t>
-        </is>
-      </c>
+      <c r="E195" t="inlineStr"/>
       <c r="F195" t="inlineStr"/>
       <c r="G195" t="inlineStr"/>
       <c r="H195" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=24.5639781,-81.727061</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=28.4918618,-82.6504993</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/3067883937</t>
+          <t>https://www.openstreetmap.org/way/1253511889</t>
         </is>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>Sunset Marina</t>
+          <t>Tarpon Point Marina</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -6755,28 +6767,24 @@
       </c>
       <c r="C196" t="inlineStr"/>
       <c r="D196" t="inlineStr"/>
-      <c r="E196" t="inlineStr">
-        <is>
-          <t>http://www.sunsetmarinakw.com/</t>
-        </is>
-      </c>
+      <c r="E196" t="inlineStr"/>
       <c r="F196" t="inlineStr"/>
       <c r="G196" t="inlineStr"/>
       <c r="H196" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=24.5788844,-81.7504577</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=26.5391764,-81.9998993</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/961607051</t>
+          <t>https://www.openstreetmap.org/node/7107428774</t>
         </is>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>Sunshine Key Marina</t>
+          <t>Tarpon Pointe Marina</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -6786,28 +6794,24 @@
       </c>
       <c r="C197" t="inlineStr"/>
       <c r="D197" t="inlineStr"/>
-      <c r="E197" t="inlineStr">
-        <is>
-          <t>http://www.rvonthego.com/florida/sunshine-key-rv-resort-marina/?utm_source=yext&amp;utm_medium=directory&amp;utm_campaign=Yext%20Directory%20Listing</t>
-        </is>
-      </c>
+      <c r="E197" t="inlineStr"/>
       <c r="F197" t="inlineStr"/>
       <c r="G197" t="inlineStr"/>
       <c r="H197" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=24.6726077,-81.2484539</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=27.4974285,-82.556367</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/494903704</t>
+          <t>https://www.openstreetmap.org/way/895995819</t>
         </is>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>Tarpon Point Marina</t>
+          <t>Tarpon Springs City Marina</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -6822,19 +6826,19 @@
       <c r="G198" t="inlineStr"/>
       <c r="H198" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=26.5391764,-81.9998993</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=28.1558516,-82.7579354</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/7107428774</t>
+          <t>https://www.openstreetmap.org/node/13333909077</t>
         </is>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>Tarpon Pointe Marina</t>
+          <t>Titusville Marina</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -6849,19 +6853,19 @@
       <c r="G199" t="inlineStr"/>
       <c r="H199" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=27.4974285,-82.556367</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=28.6200871,-80.8088078</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/895995819</t>
+          <t>https://www.openstreetmap.org/node/1668212384</t>
         </is>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>Tarpon Springs City Marina</t>
+          <t>Tween Waters Marina</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -6876,19 +6880,19 @@
       <c r="G200" t="inlineStr"/>
       <c r="H200" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=28.1558516,-82.7579354</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=26.5104729,-82.1890847</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/13333909077</t>
+          <t>https://www.openstreetmap.org/node/2144697314</t>
         </is>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>Titusville Marina</t>
+          <t>Twin Dolphin Marina</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -6903,19 +6907,19 @@
       <c r="G201" t="inlineStr"/>
       <c r="H201" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=28.6200871,-80.8088078</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=27.5000799,-82.573279</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/1668212384</t>
+          <t>https://www.openstreetmap.org/way/496739743</t>
         </is>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>Tween Waters Marina</t>
+          <t>USF Haney Landing Sailing Cener</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -6930,19 +6934,19 @@
       <c r="G202" t="inlineStr"/>
       <c r="H202" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=26.5104729,-82.1890847</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=27.7619064,-82.6348134</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/2144697314</t>
+          <t>https://www.openstreetmap.org/way/1463793071</t>
         </is>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>Twin Dolphin Marina</t>
+          <t>Venetian Cove Marina</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -6957,19 +6961,19 @@
       <c r="G203" t="inlineStr"/>
       <c r="H203" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=27.5000799,-82.573279</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=28.8046919,-81.8716146</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/496739743</t>
+          <t>https://www.openstreetmap.org/way/560378213</t>
         </is>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>USF Haney Landing Sailing Cener</t>
+          <t>Vinoy Marina</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -6984,19 +6988,19 @@
       <c r="G204" t="inlineStr"/>
       <c r="H204" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=27.7619064,-82.6348134</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=27.7771572,-82.6288077</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/1463793071</t>
+          <t>https://www.openstreetmap.org/way/1463793063</t>
         </is>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>Venetian Cove Marina</t>
+          <t>Walt Disney World Watercraft Marina &amp; Drydock</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -7007,23 +7011,31 @@
       <c r="C205" t="inlineStr"/>
       <c r="D205" t="inlineStr"/>
       <c r="E205" t="inlineStr"/>
-      <c r="F205" t="inlineStr"/>
-      <c r="G205" t="inlineStr"/>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>1280 Facilities Way, Bay Lake, FL 32836</t>
+        </is>
+      </c>
+      <c r="G205" t="inlineStr">
+        <is>
+          <t>Bay Lake</t>
+        </is>
+      </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=28.8046919,-81.8716146</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=28.424702,-81.5736382</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/560378213</t>
+          <t>https://www.openstreetmap.org/way/578705041</t>
         </is>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>Vinoy Marina</t>
+          <t>Waterfront</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -7038,19 +7050,19 @@
       <c r="G206" t="inlineStr"/>
       <c r="H206" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=27.7771572,-82.6288077</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=27.7133521,-82.68303</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/1463793063</t>
+          <t>https://www.openstreetmap.org/way/473381996</t>
         </is>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>Walker's Hideaway Marina of Marco Island</t>
+          <t>Wekiva Marina</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -7060,28 +7072,24 @@
       </c>
       <c r="C207" t="inlineStr"/>
       <c r="D207" t="inlineStr"/>
-      <c r="E207" t="inlineStr">
-        <is>
-          <t>http://www.walkersmarine.com/</t>
-        </is>
-      </c>
+      <c r="E207" t="inlineStr"/>
       <c r="F207" t="inlineStr"/>
       <c r="G207" t="inlineStr"/>
       <c r="H207" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=25.9568533,-81.7217535</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=28.7135391,-81.4443333</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/5482408657</t>
+          <t>https://www.openstreetmap.org/node/1817980857</t>
         </is>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>Walt Disney World Watercraft Marina &amp; Drydock</t>
+          <t>Wilderness Lodge Marina</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -7092,31 +7100,23 @@
       <c r="C208" t="inlineStr"/>
       <c r="D208" t="inlineStr"/>
       <c r="E208" t="inlineStr"/>
-      <c r="F208" t="inlineStr">
-        <is>
-          <t>1280 Facilities Way, Bay Lake, FL 32836</t>
-        </is>
-      </c>
-      <c r="G208" t="inlineStr">
-        <is>
-          <t>Bay Lake</t>
-        </is>
-      </c>
+      <c r="F208" t="inlineStr"/>
+      <c r="G208" t="inlineStr"/>
       <c r="H208" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=28.424702,-81.5736382</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=28.4093956,-81.5702804</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/578705041</t>
+          <t>https://www.openstreetmap.org/way/344805079</t>
         </is>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>Waterfront</t>
+          <t>Yacht Harbor Marina</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -7131,19 +7131,19 @@
       <c r="G209" t="inlineStr"/>
       <c r="H209" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=27.7133521,-82.68303</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=29.5759948,-81.1885031</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/way/473381996</t>
+          <t>https://www.openstreetmap.org/way/1383214862</t>
         </is>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>Wekiva Marina</t>
+          <t>Yacht Harbour Marina</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -7158,129 +7158,17 @@
       <c r="G210" t="inlineStr"/>
       <c r="H210" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=28.7135391,-81.4443333</t>
+          <t>https://www.google.com/maps/search/?api=1&amp;query=26.5478091,-82.1967413</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>https://www.openstreetmap.org/node/1817980857</t>
-        </is>
-      </c>
-    </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>Whale Harbor Marina</t>
-        </is>
-      </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>Marina / docks</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr"/>
-      <c r="D211" t="inlineStr"/>
-      <c r="E211" t="inlineStr">
-        <is>
-          <t>https://whaleharbormarina.com/</t>
-        </is>
-      </c>
-      <c r="F211" t="inlineStr"/>
-      <c r="G211" t="inlineStr"/>
-      <c r="H211" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=24.9364501,-80.6121534</t>
-        </is>
-      </c>
-      <c r="I211" t="inlineStr">
-        <is>
-          <t>https://www.openstreetmap.org/node/3058734957</t>
-        </is>
-      </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>Wilderness Lodge Marina</t>
-        </is>
-      </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>Marina / docks</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr"/>
-      <c r="D212" t="inlineStr"/>
-      <c r="E212" t="inlineStr"/>
-      <c r="F212" t="inlineStr"/>
-      <c r="G212" t="inlineStr"/>
-      <c r="H212" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=28.4093956,-81.5702804</t>
-        </is>
-      </c>
-      <c r="I212" t="inlineStr">
-        <is>
-          <t>https://www.openstreetmap.org/way/344805079</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>Yacht Harbor Marina</t>
-        </is>
-      </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>Marina / docks</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr"/>
-      <c r="D213" t="inlineStr"/>
-      <c r="E213" t="inlineStr"/>
-      <c r="F213" t="inlineStr"/>
-      <c r="G213" t="inlineStr"/>
-      <c r="H213" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=29.5759948,-81.1885031</t>
-        </is>
-      </c>
-      <c r="I213" t="inlineStr">
-        <is>
-          <t>https://www.openstreetmap.org/way/1383214862</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>Yacht Harbour Marina</t>
-        </is>
-      </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>Marina / docks</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr"/>
-      <c r="D214" t="inlineStr"/>
-      <c r="E214" t="inlineStr"/>
-      <c r="F214" t="inlineStr"/>
-      <c r="G214" t="inlineStr"/>
-      <c r="H214" t="inlineStr">
-        <is>
-          <t>https://www.google.com/maps/search/?api=1&amp;query=26.5478091,-82.1967413</t>
-        </is>
-      </c>
-      <c r="I214" t="inlineStr">
-        <is>
           <t>https://www.openstreetmap.org/way/1342263875</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I214"/>
+  <autoFilter ref="A1:I210"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>